--- a/template.xlsx
+++ b/template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Studio3/Desktop/PM Reports/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Studio3/Desktop/PM Reports/Streamlit App/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEE13E3C-98EB-364C-BF60-7EFD685B9BF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6B7D248-E1AC-FB49-91E0-C2806E2B9983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4440" yWindow="3980" windowWidth="28800" windowHeight="17500" activeTab="1" xr2:uid="{C1D30A1A-AE12-9A4B-A39A-04F2223DCEBD}"/>
+    <workbookView xWindow="-20" yWindow="500" windowWidth="28800" windowHeight="16500" activeTab="1" xr2:uid="{C1D30A1A-AE12-9A4B-A39A-04F2223DCEBD}"/>
   </bookViews>
   <sheets>
     <sheet name="Transactions" sheetId="62" r:id="rId1"/>
@@ -720,12 +720,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_([$$-409]* #,##0.00_);_([$$-409]* \(#,##0.00\);_([$$-409]* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="mm/dd/yy;@"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
   <fonts count="49">
     <font>
@@ -2339,9 +2340,6 @@
     <xf numFmtId="9" fontId="34" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="34" fillId="0" borderId="10" xfId="44" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="34" fillId="0" borderId="10" xfId="44" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2619,6 +2617,12 @@
     <xf numFmtId="166" fontId="28" fillId="39" borderId="20" xfId="45" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="166" fontId="34" fillId="0" borderId="0" xfId="45" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="34" fillId="0" borderId="20" xfId="45" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="166" fontId="35" fillId="33" borderId="0" xfId="45" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2661,12 +2665,6 @@
     <xf numFmtId="166" fontId="34" fillId="33" borderId="20" xfId="45" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="34" fillId="0" borderId="0" xfId="45" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="34" fillId="0" borderId="20" xfId="45" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="166" fontId="34" fillId="0" borderId="0" xfId="45" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2687,6 +2685,9 @@
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="34" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="46">
@@ -2740,11 +2741,7 @@
   <dxfs count="45">
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
@@ -2754,28 +2751,13 @@
         <name val="Gilroy-Regular"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <numFmt numFmtId="13" formatCode="0%"/>
       <fill>
         <patternFill patternType="none">
-          <fgColor indexed="64"/>
           <bgColor auto="1"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
+      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -3058,7 +3040,11 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i/>
         <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
@@ -3068,12 +3054,28 @@
         <name val="Gilroy-Regular"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
       <fill>
         <patternFill patternType="none">
+          <fgColor indexed="64"/>
           <bgColor auto="1"/>
         </patternFill>
       </fill>
-      <alignment vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -3599,11 +3601,11 @@
     <tableColumn id="3" xr3:uid="{016AFB74-23F9-5B40-B34F-AD5179EB2C2F}" name="Total Labor_x000a_Award" dataDxfId="37"/>
     <tableColumn id="4" xr3:uid="{FE941C46-3F8C-614D-9C61-D7C1D611D2DA}" name="Incurred _x000a_Labor Period of Performance" dataDxfId="36"/>
     <tableColumn id="9" xr3:uid="{0929DCDE-F89B-CE4A-9D5E-D0FF11091DE1}" name="Incurred _x000a_Labor Project To Date" dataDxfId="35"/>
-    <tableColumn id="5" xr3:uid="{021F965E-2E12-DE48-88C9-23AD55A2A3A1}" name="Remaining _x000a_Labor" dataDxfId="0">
+    <tableColumn id="5" xr3:uid="{021F965E-2E12-DE48-88C9-23AD55A2A3A1}" name="Remaining _x000a_Labor" dataDxfId="34">
       <calculatedColumnFormula>D10-F10</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{F1AA0EB8-CA0D-6E49-9B06-5403DD0FE5A9}" name="% Labor Utilized_x000a_(automated)" dataDxfId="34">
-      <calculatedColumnFormula>E10/D10</calculatedColumnFormula>
+    <tableColumn id="6" xr3:uid="{F1AA0EB8-CA0D-6E49-9B06-5403DD0FE5A9}" name="% Labor Utilized_x000a_(automated)" dataDxfId="0">
+      <calculatedColumnFormula>F10/D10</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{416943EB-7810-B54B-ADC1-F6F5CC1E6C83}" name="% Earned Value_x000a_(manual)" dataDxfId="33"/>
     <tableColumn id="8" xr3:uid="{5AFAE1F3-23A5-AE4C-B79C-60642E6F7EAA}" name="Remaining Work / Flags" dataDxfId="32"/>
@@ -73567,28 +73569,28 @@
   <sheetData>
     <row r="1" spans="1:15" ht="8" customHeight="1"/>
     <row r="2" spans="1:15" ht="15" customHeight="1">
-      <c r="B2" s="161" t="s">
+      <c r="B2" s="160" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="161"/>
-      <c r="D2" s="161"/>
-      <c r="E2" s="161"/>
-      <c r="F2" s="161"/>
-      <c r="G2" s="161"/>
-      <c r="H2" s="161"/>
-      <c r="I2" s="161"/>
-      <c r="J2" s="161"/>
+      <c r="C2" s="160"/>
+      <c r="D2" s="160"/>
+      <c r="E2" s="160"/>
+      <c r="F2" s="160"/>
+      <c r="G2" s="160"/>
+      <c r="H2" s="160"/>
+      <c r="I2" s="160"/>
+      <c r="J2" s="160"/>
     </row>
     <row r="3" spans="1:15" ht="15" customHeight="1">
-      <c r="B3" s="161"/>
-      <c r="C3" s="161"/>
-      <c r="D3" s="161"/>
-      <c r="E3" s="161"/>
-      <c r="F3" s="161"/>
-      <c r="G3" s="161"/>
-      <c r="H3" s="161"/>
-      <c r="I3" s="161"/>
-      <c r="J3" s="161"/>
+      <c r="B3" s="160"/>
+      <c r="C3" s="160"/>
+      <c r="D3" s="160"/>
+      <c r="E3" s="160"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="160"/>
+      <c r="H3" s="160"/>
+      <c r="I3" s="160"/>
+      <c r="J3" s="160"/>
     </row>
     <row r="4" spans="1:15" ht="12" customHeight="1">
       <c r="B4" s="57"/>
@@ -73602,61 +73604,61 @@
       <c r="J4" s="57"/>
     </row>
     <row r="5" spans="1:15" ht="16">
-      <c r="B5" s="137"/>
-      <c r="C5" s="137"/>
-      <c r="D5" s="138" t="s">
+      <c r="B5" s="136"/>
+      <c r="C5" s="136"/>
+      <c r="D5" s="137" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="137"/>
-      <c r="F5" s="137"/>
-      <c r="G5" s="137"/>
-      <c r="H5" s="139" t="s">
+      <c r="E5" s="136"/>
+      <c r="F5" s="136"/>
+      <c r="G5" s="136"/>
+      <c r="H5" s="138" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="137"/>
-      <c r="J5" s="137"/>
+      <c r="I5" s="136"/>
+      <c r="J5" s="136"/>
     </row>
     <row r="6" spans="1:15" ht="16">
-      <c r="B6" s="137"/>
-      <c r="C6" s="137"/>
-      <c r="D6" s="138" t="s">
+      <c r="B6" s="136"/>
+      <c r="C6" s="136"/>
+      <c r="D6" s="137" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="137"/>
-      <c r="F6" s="137"/>
-      <c r="G6" s="137"/>
-      <c r="H6" s="139" t="s">
+      <c r="E6" s="136"/>
+      <c r="F6" s="136"/>
+      <c r="G6" s="136"/>
+      <c r="H6" s="138" t="s">
         <v>24</v>
       </c>
-      <c r="I6" s="140">
+      <c r="I6" s="139">
         <f ca="1">TODAY()</f>
-        <v>46142</v>
+        <v>46143</v>
       </c>
-      <c r="J6" s="137"/>
+      <c r="J6" s="136"/>
     </row>
     <row r="7" spans="1:15" ht="8" customHeight="1">
-      <c r="B7" s="137"/>
-      <c r="C7" s="141"/>
-      <c r="D7" s="137"/>
-      <c r="E7" s="137"/>
-      <c r="F7" s="137"/>
-      <c r="G7" s="137"/>
-      <c r="H7" s="137"/>
-      <c r="I7" s="137"/>
-      <c r="J7" s="137"/>
+      <c r="B7" s="136"/>
+      <c r="C7" s="140"/>
+      <c r="D7" s="136"/>
+      <c r="E7" s="136"/>
+      <c r="F7" s="136"/>
+      <c r="G7" s="136"/>
+      <c r="H7" s="136"/>
+      <c r="I7" s="136"/>
+      <c r="J7" s="136"/>
     </row>
     <row r="8" spans="1:15" ht="21" customHeight="1">
-      <c r="B8" s="166" t="s">
+      <c r="B8" s="165" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="166"/>
-      <c r="D8" s="166"/>
-      <c r="E8" s="166"/>
-      <c r="F8" s="166"/>
-      <c r="G8" s="166"/>
-      <c r="H8" s="166"/>
-      <c r="I8" s="166"/>
-      <c r="J8" s="166"/>
+      <c r="C8" s="165"/>
+      <c r="D8" s="165"/>
+      <c r="E8" s="165"/>
+      <c r="F8" s="165"/>
+      <c r="G8" s="165"/>
+      <c r="H8" s="165"/>
+      <c r="I8" s="165"/>
+      <c r="J8" s="165"/>
     </row>
     <row r="9" spans="1:15" s="50" customFormat="1" ht="56" customHeight="1">
       <c r="B9" s="59" t="s">
@@ -73693,18 +73695,18 @@
       <c r="B10" s="91"/>
       <c r="C10" s="92"/>
       <c r="D10" s="93"/>
-      <c r="E10" s="94"/>
-      <c r="F10" s="94"/>
+      <c r="E10" s="212"/>
+      <c r="F10" s="212"/>
       <c r="G10" s="93">
         <f t="shared" ref="G10:G14" si="0">D10-F10</f>
         <v>0</v>
       </c>
       <c r="H10" s="95" t="e">
-        <f>E10/D10</f>
+        <f t="shared" ref="H10:H14" si="1">F10/D10</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I10" s="95">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J10" s="92"/>
       <c r="K10" s="53"/>
@@ -73721,14 +73723,14 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H11" s="96" t="e">
-        <f>E11/D11</f>
+      <c r="H11" s="95" t="e">
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I11" s="95">
         <v>0</v>
       </c>
-      <c r="J11" s="97"/>
+      <c r="J11" s="96"/>
     </row>
     <row r="12" spans="1:15" ht="24" customHeight="1">
       <c r="A12" s="55"/>
@@ -73741,8 +73743,8 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H12" s="96" t="e">
-        <f>E12/D12</f>
+      <c r="H12" s="95" t="e">
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I12" s="95">
@@ -73760,8 +73762,8 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H13" s="96" t="e">
-        <f>E13/D13</f>
+      <c r="H13" s="95" t="e">
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I13" s="95">
@@ -73780,35 +73782,35 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H14" s="96" t="e">
-        <f>E14/D14</f>
+      <c r="H14" s="95" t="e">
+        <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I14" s="95">
         <v>0</v>
       </c>
-      <c r="J14" s="97"/>
+      <c r="J14" s="96"/>
       <c r="L14" s="87"/>
       <c r="M14" s="87"/>
       <c r="O14" s="51"/>
     </row>
     <row r="15" spans="1:15" s="56" customFormat="1" ht="15">
-      <c r="B15" s="142" t="s">
+      <c r="B15" s="141" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="143"/>
-      <c r="D15" s="144">
+      <c r="C15" s="142"/>
+      <c r="D15" s="143">
         <f>SUBTOTAL(109,Table2[Total Labor
 Award])</f>
         <v>0</v>
       </c>
-      <c r="E15" s="144">
+      <c r="E15" s="143">
         <f>SUBTOTAL(109,Table2[Incurred 
 Labor Period of Performance])</f>
         <v>0</v>
       </c>
-      <c r="F15" s="144"/>
-      <c r="G15" s="144">
+      <c r="F15" s="143"/>
+      <c r="G15" s="143">
         <f>SUBTOTAL(109,Table2[Remaining 
 Labor])</f>
         <v>0</v>
@@ -73821,48 +73823,48 @@
         <f>((I10*D10)+(I11*D11)+(I12*D12)+(I13*D13)+(I14*D14))/D15</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J15" s="142"/>
+      <c r="J15" s="141"/>
       <c r="K15" s="88"/>
       <c r="L15" s="89"/>
     </row>
     <row r="16" spans="1:15">
-      <c r="B16" s="145"/>
-      <c r="C16" s="146"/>
-      <c r="D16" s="145"/>
-      <c r="E16" s="145"/>
-      <c r="F16" s="145"/>
-      <c r="G16" s="145"/>
-      <c r="H16" s="145"/>
-      <c r="I16" s="145"/>
-      <c r="J16" s="145"/>
+      <c r="B16" s="144"/>
+      <c r="C16" s="145"/>
+      <c r="D16" s="144"/>
+      <c r="E16" s="144"/>
+      <c r="F16" s="144"/>
+      <c r="G16" s="144"/>
+      <c r="H16" s="144"/>
+      <c r="I16" s="144"/>
+      <c r="J16" s="144"/>
       <c r="L16" s="87"/>
     </row>
     <row r="17" spans="1:14">
-      <c r="B17" s="145"/>
-      <c r="C17" s="146"/>
-      <c r="D17" s="145"/>
-      <c r="E17" s="147"/>
-      <c r="F17" s="147"/>
-      <c r="G17" s="145"/>
-      <c r="H17" s="145"/>
-      <c r="I17" s="145"/>
-      <c r="J17" s="145"/>
+      <c r="B17" s="144"/>
+      <c r="C17" s="145"/>
+      <c r="D17" s="144"/>
+      <c r="E17" s="146"/>
+      <c r="F17" s="146"/>
+      <c r="G17" s="144"/>
+      <c r="H17" s="144"/>
+      <c r="I17" s="144"/>
+      <c r="J17" s="144"/>
       <c r="L17" s="87"/>
     </row>
     <row r="18" spans="1:14" ht="19" customHeight="1">
-      <c r="B18" s="162" t="s">
+      <c r="B18" s="161" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="163"/>
-      <c r="D18" s="163"/>
-      <c r="E18" s="163"/>
-      <c r="F18" s="158"/>
+      <c r="C18" s="162"/>
+      <c r="D18" s="162"/>
+      <c r="E18" s="162"/>
+      <c r="F18" s="157"/>
       <c r="G18" s="85"/>
-      <c r="H18" s="166" t="s">
+      <c r="H18" s="165" t="s">
         <v>35</v>
       </c>
-      <c r="I18" s="166"/>
-      <c r="J18" s="137"/>
+      <c r="I18" s="165"/>
+      <c r="J18" s="136"/>
       <c r="K18" s="83"/>
       <c r="L18" s="83"/>
       <c r="M18" s="83"/>
@@ -73875,31 +73877,31 @@
       <c r="C19" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="168" t="s">
+      <c r="D19" s="167" t="s">
         <v>38</v>
       </c>
-      <c r="E19" s="169"/>
-      <c r="F19" s="159"/>
+      <c r="E19" s="168"/>
+      <c r="F19" s="158"/>
       <c r="G19" s="86"/>
-      <c r="H19" s="167">
+      <c r="H19" s="166">
         <f>E15+C20</f>
         <v>0</v>
       </c>
-      <c r="I19" s="167"/>
-      <c r="J19" s="137"/>
+      <c r="I19" s="166"/>
+      <c r="J19" s="136"/>
       <c r="L19" s="87"/>
     </row>
     <row r="20" spans="1:14" ht="26" customHeight="1">
       <c r="A20" s="55"/>
       <c r="B20" s="84"/>
       <c r="C20" s="90"/>
-      <c r="D20" s="164"/>
-      <c r="E20" s="165"/>
-      <c r="F20" s="160"/>
-      <c r="G20" s="148"/>
-      <c r="H20" s="149"/>
-      <c r="I20" s="150"/>
-      <c r="J20" s="151"/>
+      <c r="D20" s="163"/>
+      <c r="E20" s="164"/>
+      <c r="F20" s="159"/>
+      <c r="G20" s="147"/>
+      <c r="H20" s="148"/>
+      <c r="I20" s="149"/>
+      <c r="J20" s="150"/>
       <c r="L20" s="87"/>
       <c r="M20" s="87"/>
     </row>
@@ -74064,71 +74066,71 @@
   <dimension ref="B1:K39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="2" style="157" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" style="157" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" style="157" customWidth="1"/>
-    <col min="4" max="4" width="20.33203125" style="157" customWidth="1"/>
-    <col min="5" max="5" width="15.1640625" style="157" customWidth="1"/>
-    <col min="6" max="6" width="3.6640625" style="157" customWidth="1"/>
-    <col min="7" max="7" width="21.5" style="157" customWidth="1"/>
-    <col min="8" max="11" width="14.83203125" style="157" customWidth="1"/>
-    <col min="12" max="16384" width="8.83203125" style="157"/>
+    <col min="1" max="1" width="2" style="156" customWidth="1"/>
+    <col min="2" max="2" width="7.33203125" style="156" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" style="156" customWidth="1"/>
+    <col min="4" max="4" width="20.33203125" style="156" customWidth="1"/>
+    <col min="5" max="5" width="15.1640625" style="156" customWidth="1"/>
+    <col min="6" max="6" width="3.6640625" style="156" customWidth="1"/>
+    <col min="7" max="7" width="21.5" style="156" customWidth="1"/>
+    <col min="8" max="11" width="14.83203125" style="156" customWidth="1"/>
+    <col min="12" max="16384" width="8.83203125" style="156"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" s="137" customFormat="1" ht="8" customHeight="1">
-      <c r="C1" s="141"/>
-      <c r="J1" s="152"/>
-      <c r="K1" s="153"/>
-    </row>
-    <row r="2" spans="2:11" s="137" customFormat="1" ht="15" customHeight="1">
-      <c r="B2" s="161" t="s">
+    <row r="1" spans="2:11" s="136" customFormat="1" ht="8" customHeight="1">
+      <c r="C1" s="140"/>
+      <c r="J1" s="151"/>
+      <c r="K1" s="152"/>
+    </row>
+    <row r="2" spans="2:11" s="136" customFormat="1" ht="15" customHeight="1">
+      <c r="B2" s="160" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="161"/>
-      <c r="D2" s="161"/>
-      <c r="E2" s="161"/>
-      <c r="F2" s="161"/>
-      <c r="G2" s="161"/>
-      <c r="H2" s="161"/>
-      <c r="I2" s="161"/>
-      <c r="J2" s="161"/>
-      <c r="K2" s="161"/>
-    </row>
-    <row r="3" spans="2:11" s="137" customFormat="1" ht="15" customHeight="1">
-      <c r="B3" s="161"/>
-      <c r="C3" s="161"/>
-      <c r="D3" s="161"/>
-      <c r="E3" s="161"/>
-      <c r="F3" s="161"/>
-      <c r="G3" s="161"/>
-      <c r="H3" s="161"/>
-      <c r="I3" s="161"/>
-      <c r="J3" s="161"/>
-      <c r="K3" s="161"/>
-    </row>
-    <row r="4" spans="2:11" s="137" customFormat="1" ht="12" customHeight="1">
-      <c r="B4" s="154"/>
-      <c r="C4" s="154"/>
-      <c r="D4" s="154"/>
-      <c r="E4" s="154"/>
-      <c r="F4" s="154"/>
-      <c r="G4" s="154"/>
-      <c r="H4" s="155"/>
-      <c r="I4" s="154"/>
-      <c r="J4" s="154"/>
-      <c r="K4" s="154"/>
-    </row>
-    <row r="5" spans="2:11" s="137" customFormat="1" ht="16" customHeight="1">
-      <c r="B5" s="182" t="s">
+      <c r="C2" s="160"/>
+      <c r="D2" s="160"/>
+      <c r="E2" s="160"/>
+      <c r="F2" s="160"/>
+      <c r="G2" s="160"/>
+      <c r="H2" s="160"/>
+      <c r="I2" s="160"/>
+      <c r="J2" s="160"/>
+      <c r="K2" s="160"/>
+    </row>
+    <row r="3" spans="2:11" s="136" customFormat="1" ht="15" customHeight="1">
+      <c r="B3" s="160"/>
+      <c r="C3" s="160"/>
+      <c r="D3" s="160"/>
+      <c r="E3" s="160"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="160"/>
+      <c r="H3" s="160"/>
+      <c r="I3" s="160"/>
+      <c r="J3" s="160"/>
+      <c r="K3" s="160"/>
+    </row>
+    <row r="4" spans="2:11" s="136" customFormat="1" ht="12" customHeight="1">
+      <c r="B4" s="153"/>
+      <c r="C4" s="153"/>
+      <c r="D4" s="153"/>
+      <c r="E4" s="153"/>
+      <c r="F4" s="153"/>
+      <c r="G4" s="153"/>
+      <c r="H4" s="154"/>
+      <c r="I4" s="153"/>
+      <c r="J4" s="153"/>
+      <c r="K4" s="153"/>
+    </row>
+    <row r="5" spans="2:11" s="136" customFormat="1" ht="16" customHeight="1">
+      <c r="B5" s="181" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="182"/>
+      <c r="C5" s="181"/>
       <c r="D5" s="69">
         <f>'Account Overview'!E5</f>
         <v>0</v>
       </c>
-      <c r="E5" s="156"/>
-      <c r="F5" s="156"/>
+      <c r="E5" s="155"/>
+      <c r="F5" s="155"/>
       <c r="G5" s="70" t="s">
         <v>22</v>
       </c>
@@ -74137,50 +74139,50 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:11" s="137" customFormat="1" ht="17" customHeight="1">
-      <c r="B6" s="182" t="s">
+    <row r="6" spans="2:11" s="136" customFormat="1" ht="17" customHeight="1">
+      <c r="B6" s="181" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="182"/>
+      <c r="C6" s="181"/>
       <c r="D6" s="69">
         <f>'Account Overview'!E6</f>
         <v>0</v>
       </c>
-      <c r="E6" s="156"/>
-      <c r="F6" s="156"/>
+      <c r="E6" s="155"/>
+      <c r="F6" s="155"/>
       <c r="G6" s="70" t="s">
         <v>24</v>
       </c>
-      <c r="H6" s="136">
+      <c r="H6" s="135">
         <f ca="1">TODAY()</f>
-        <v>46142</v>
+        <v>46143</v>
       </c>
     </row>
-    <row r="7" spans="2:11" s="137" customFormat="1" ht="8" customHeight="1" thickBot="1">
+    <row r="7" spans="2:11" s="136" customFormat="1" ht="8" customHeight="1" thickBot="1">
       <c r="B7" s="69"/>
-      <c r="C7" s="106"/>
+      <c r="C7" s="105"/>
       <c r="D7" s="69"/>
       <c r="E7" s="69"/>
       <c r="F7" s="69"/>
-      <c r="G7" s="156"/>
-      <c r="J7" s="152"/>
-      <c r="K7" s="153"/>
+      <c r="G7" s="155"/>
+      <c r="J7" s="151"/>
+      <c r="K7" s="152"/>
     </row>
     <row r="8" spans="2:11">
-      <c r="B8" s="176" t="s">
+      <c r="B8" s="175" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="177"/>
-      <c r="D8" s="177"/>
-      <c r="E8" s="178"/>
+      <c r="C8" s="176"/>
+      <c r="D8" s="176"/>
+      <c r="E8" s="177"/>
       <c r="F8" s="69"/>
-      <c r="G8" s="176" t="s">
+      <c r="G8" s="175" t="s">
         <v>40</v>
       </c>
-      <c r="H8" s="177"/>
-      <c r="I8" s="177"/>
-      <c r="J8" s="177"/>
-      <c r="K8" s="178"/>
+      <c r="H8" s="176"/>
+      <c r="I8" s="176"/>
+      <c r="J8" s="176"/>
+      <c r="K8" s="177"/>
     </row>
     <row r="9" spans="2:11">
       <c r="B9" s="71" t="s">
@@ -74197,19 +74199,19 @@
         <v>0</v>
       </c>
       <c r="F9" s="69"/>
-      <c r="G9" s="131" t="s">
+      <c r="G9" s="130" t="s">
         <v>43</v>
       </c>
-      <c r="H9" s="132" t="s">
+      <c r="H9" s="131" t="s">
         <v>44</v>
       </c>
-      <c r="I9" s="133" t="s">
+      <c r="I9" s="132" t="s">
         <v>45</v>
       </c>
-      <c r="J9" s="134" t="s">
+      <c r="J9" s="133" t="s">
         <v>46</v>
       </c>
-      <c r="K9" s="135" t="s">
+      <c r="K9" s="134" t="s">
         <v>47</v>
       </c>
     </row>
@@ -74225,19 +74227,19 @@
       </c>
       <c r="E10" s="77">
         <f ca="1">DATEDIF(C9,C11,"d")/7</f>
-        <v>16.857142857142858</v>
+        <v>17</v>
       </c>
       <c r="F10" s="69"/>
       <c r="G10" s="75" t="s">
         <v>50</v>
       </c>
-      <c r="H10" s="124"/>
-      <c r="I10" s="124"/>
-      <c r="J10" s="126">
+      <c r="H10" s="123"/>
+      <c r="I10" s="123"/>
+      <c r="J10" s="125">
         <f t="shared" ref="J10:J16" si="0">H10-I10</f>
         <v>0</v>
       </c>
-      <c r="K10" s="127">
+      <c r="K10" s="126">
         <v>0</v>
       </c>
     </row>
@@ -74247,7 +74249,7 @@
       </c>
       <c r="C11" s="79">
         <f ca="1">TODAY()</f>
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="D11" s="70" t="s">
         <v>52</v>
@@ -74260,21 +74262,21 @@
       <c r="G11" s="75" t="s">
         <v>53</v>
       </c>
-      <c r="H11" s="124"/>
-      <c r="I11" s="124"/>
-      <c r="J11" s="126">
+      <c r="H11" s="123"/>
+      <c r="I11" s="123"/>
+      <c r="J11" s="125">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K11" s="127">
+      <c r="K11" s="126">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:11">
-      <c r="B12" s="170" t="s">
+      <c r="B12" s="169" t="s">
         <v>54</v>
       </c>
-      <c r="C12" s="171"/>
+      <c r="C12" s="170"/>
       <c r="D12" s="73" t="s">
         <v>55</v>
       </c>
@@ -74286,19 +74288,19 @@
       <c r="G12" s="75" t="s">
         <v>56</v>
       </c>
-      <c r="H12" s="125"/>
-      <c r="I12" s="124"/>
-      <c r="J12" s="126">
+      <c r="H12" s="124"/>
+      <c r="I12" s="123"/>
+      <c r="J12" s="125">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K12" s="127">
+      <c r="K12" s="126">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="2:11">
-      <c r="B13" s="172"/>
-      <c r="C13" s="173"/>
+      <c r="B13" s="171"/>
+      <c r="C13" s="172"/>
       <c r="D13" s="69" t="s">
         <v>57</v>
       </c>
@@ -74310,19 +74312,19 @@
       <c r="G13" s="75" t="s">
         <v>58</v>
       </c>
-      <c r="H13" s="125"/>
-      <c r="I13" s="124"/>
-      <c r="J13" s="126">
+      <c r="H13" s="124"/>
+      <c r="I13" s="123"/>
+      <c r="J13" s="125">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K13" s="127">
+      <c r="K13" s="126">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="2:11" ht="17" thickBot="1">
-      <c r="B14" s="174"/>
-      <c r="C14" s="175"/>
+      <c r="B14" s="173"/>
+      <c r="C14" s="174"/>
       <c r="D14" s="81" t="s">
         <v>52</v>
       </c>
@@ -74334,13 +74336,13 @@
       <c r="G14" s="75" t="s">
         <v>59</v>
       </c>
-      <c r="H14" s="125"/>
-      <c r="I14" s="124"/>
-      <c r="J14" s="126">
+      <c r="H14" s="124"/>
+      <c r="I14" s="123"/>
+      <c r="J14" s="125">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K14" s="127">
+      <c r="K14" s="126">
         <v>0</v>
       </c>
     </row>
@@ -74353,13 +74355,13 @@
       <c r="G15" s="75" t="s">
         <v>60</v>
       </c>
-      <c r="H15" s="124"/>
-      <c r="I15" s="124"/>
-      <c r="J15" s="126">
+      <c r="H15" s="123"/>
+      <c r="I15" s="123"/>
+      <c r="J15" s="125">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K15" s="127">
+      <c r="K15" s="126">
         <v>0</v>
       </c>
     </row>
@@ -74368,56 +74370,56 @@
       <c r="G16" s="75" t="s">
         <v>61</v>
       </c>
-      <c r="H16" s="124"/>
-      <c r="I16" s="124"/>
-      <c r="J16" s="126">
+      <c r="H16" s="123"/>
+      <c r="I16" s="123"/>
+      <c r="J16" s="125">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K16" s="127">
+      <c r="K16" s="126">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:11" ht="17" thickBot="1">
       <c r="F17" s="69"/>
-      <c r="G17" s="129" t="s">
+      <c r="G17" s="128" t="s">
         <v>62</v>
       </c>
-      <c r="H17" s="130">
+      <c r="H17" s="129">
         <f>SUM(H10:H16)</f>
         <v>0</v>
       </c>
-      <c r="I17" s="130">
+      <c r="I17" s="129">
         <f>SUM(I10:I16)</f>
         <v>0</v>
       </c>
-      <c r="J17" s="130">
+      <c r="J17" s="129">
         <f>SUM(J10:J16)</f>
         <v>0</v>
       </c>
-      <c r="K17" s="128">
+      <c r="K17" s="127">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:11" ht="17" thickBot="1">
       <c r="F18" s="69"/>
-      <c r="G18" s="156"/>
+      <c r="G18" s="155"/>
     </row>
     <row r="19" spans="2:11">
-      <c r="B19" s="176" t="s">
+      <c r="B19" s="175" t="s">
         <v>63</v>
       </c>
-      <c r="C19" s="177"/>
-      <c r="D19" s="177"/>
-      <c r="E19" s="178"/>
+      <c r="C19" s="176"/>
+      <c r="D19" s="176"/>
+      <c r="E19" s="177"/>
       <c r="F19" s="69"/>
-      <c r="G19" s="176" t="s">
+      <c r="G19" s="175" t="s">
         <v>63</v>
       </c>
-      <c r="H19" s="177"/>
-      <c r="I19" s="177"/>
-      <c r="J19" s="177"/>
-      <c r="K19" s="178"/>
+      <c r="H19" s="176"/>
+      <c r="I19" s="176"/>
+      <c r="J19" s="176"/>
+      <c r="K19" s="177"/>
     </row>
     <row r="20" spans="2:11">
       <c r="B20" s="71" t="s">
@@ -74434,19 +74436,19 @@
         <v>0</v>
       </c>
       <c r="F20" s="69"/>
-      <c r="G20" s="131" t="s">
+      <c r="G20" s="130" t="s">
         <v>43</v>
       </c>
-      <c r="H20" s="132" t="s">
+      <c r="H20" s="131" t="s">
         <v>44</v>
       </c>
-      <c r="I20" s="133" t="s">
+      <c r="I20" s="132" t="s">
         <v>45</v>
       </c>
-      <c r="J20" s="134" t="s">
+      <c r="J20" s="133" t="s">
         <v>46</v>
       </c>
-      <c r="K20" s="135" t="s">
+      <c r="K20" s="134" t="s">
         <v>47</v>
       </c>
     </row>
@@ -74462,19 +74464,19 @@
       </c>
       <c r="E21" s="77">
         <f ca="1">DATEDIF(C20,C22,"d")/7</f>
-        <v>16.857142857142858</v>
+        <v>17</v>
       </c>
       <c r="F21" s="69"/>
       <c r="G21" s="75" t="s">
         <v>50</v>
       </c>
-      <c r="H21" s="124"/>
-      <c r="I21" s="124"/>
-      <c r="J21" s="126">
+      <c r="H21" s="123"/>
+      <c r="I21" s="123"/>
+      <c r="J21" s="125">
         <f t="shared" ref="J21:J27" si="1">H21-I21</f>
         <v>0</v>
       </c>
-      <c r="K21" s="127">
+      <c r="K21" s="126">
         <v>0</v>
       </c>
     </row>
@@ -74484,7 +74486,7 @@
       </c>
       <c r="C22" s="79">
         <f ca="1">TODAY()</f>
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="D22" s="70" t="s">
         <v>52</v>
@@ -74497,21 +74499,21 @@
       <c r="G22" s="75" t="s">
         <v>53</v>
       </c>
-      <c r="H22" s="124"/>
-      <c r="I22" s="124"/>
-      <c r="J22" s="126">
+      <c r="H22" s="123"/>
+      <c r="I22" s="123"/>
+      <c r="J22" s="125">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K22" s="127">
+      <c r="K22" s="126">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="2:11">
-      <c r="B23" s="170" t="s">
+      <c r="B23" s="169" t="s">
         <v>54</v>
       </c>
-      <c r="C23" s="171"/>
+      <c r="C23" s="170"/>
       <c r="D23" s="73" t="s">
         <v>55</v>
       </c>
@@ -74522,19 +74524,19 @@
       <c r="G23" s="75" t="s">
         <v>56</v>
       </c>
-      <c r="H23" s="125"/>
-      <c r="I23" s="124"/>
-      <c r="J23" s="126">
+      <c r="H23" s="124"/>
+      <c r="I23" s="123"/>
+      <c r="J23" s="125">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K23" s="127">
+      <c r="K23" s="126">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="2:11">
-      <c r="B24" s="172"/>
-      <c r="C24" s="173"/>
+      <c r="B24" s="171"/>
+      <c r="C24" s="172"/>
       <c r="D24" s="69" t="s">
         <v>57</v>
       </c>
@@ -74545,19 +74547,19 @@
       <c r="G24" s="75" t="s">
         <v>58</v>
       </c>
-      <c r="H24" s="125"/>
-      <c r="I24" s="124"/>
-      <c r="J24" s="126">
+      <c r="H24" s="124"/>
+      <c r="I24" s="123"/>
+      <c r="J24" s="125">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K24" s="127">
+      <c r="K24" s="126">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="2:11" ht="17" thickBot="1">
-      <c r="B25" s="174"/>
-      <c r="C25" s="175"/>
+      <c r="B25" s="173"/>
+      <c r="C25" s="174"/>
       <c r="D25" s="81" t="s">
         <v>52</v>
       </c>
@@ -74568,13 +74570,13 @@
       <c r="G25" s="75" t="s">
         <v>59</v>
       </c>
-      <c r="H25" s="125"/>
-      <c r="I25" s="124"/>
-      <c r="J25" s="126">
+      <c r="H25" s="124"/>
+      <c r="I25" s="123"/>
+      <c r="J25" s="125">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K25" s="127">
+      <c r="K25" s="126">
         <v>0</v>
       </c>
     </row>
@@ -74582,13 +74584,13 @@
       <c r="G26" s="75" t="s">
         <v>60</v>
       </c>
-      <c r="H26" s="124"/>
-      <c r="I26" s="124"/>
-      <c r="J26" s="126">
+      <c r="H26" s="123"/>
+      <c r="I26" s="123"/>
+      <c r="J26" s="125">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K26" s="127">
+      <c r="K26" s="126">
         <v>0</v>
       </c>
     </row>
@@ -74596,52 +74598,52 @@
       <c r="G27" s="75" t="s">
         <v>61</v>
       </c>
-      <c r="H27" s="124"/>
-      <c r="I27" s="124"/>
-      <c r="J27" s="126">
+      <c r="H27" s="123"/>
+      <c r="I27" s="123"/>
+      <c r="J27" s="125">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K27" s="127">
+      <c r="K27" s="126">
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="2:11" ht="17" thickBot="1">
-      <c r="G28" s="129" t="s">
+      <c r="G28" s="128" t="s">
         <v>62</v>
       </c>
-      <c r="H28" s="130">
+      <c r="H28" s="129">
         <f>SUM(H21:H27)</f>
         <v>0</v>
       </c>
-      <c r="I28" s="130">
+      <c r="I28" s="129">
         <f>SUM(I21:I27)</f>
         <v>0</v>
       </c>
-      <c r="J28" s="130">
+      <c r="J28" s="129">
         <f>SUM(J21:J27)</f>
         <v>0</v>
       </c>
-      <c r="K28" s="128" t="e">
+      <c r="K28" s="127" t="e">
         <f>((K21*H21)+(K22*H22)+(K23*H23)+(K24*H24)+(K25*H25)+(K26*H26)+(K27*H27))/H28</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="29" spans="2:11" ht="17" thickBot="1"/>
     <row r="30" spans="2:11">
-      <c r="B30" s="179" t="s">
+      <c r="B30" s="178" t="s">
         <v>64</v>
       </c>
-      <c r="C30" s="180"/>
-      <c r="D30" s="180"/>
-      <c r="E30" s="181"/>
-      <c r="G30" s="176" t="s">
+      <c r="C30" s="179"/>
+      <c r="D30" s="179"/>
+      <c r="E30" s="180"/>
+      <c r="G30" s="175" t="s">
         <v>64</v>
       </c>
-      <c r="H30" s="177"/>
-      <c r="I30" s="177"/>
-      <c r="J30" s="177"/>
-      <c r="K30" s="178"/>
+      <c r="H30" s="176"/>
+      <c r="I30" s="176"/>
+      <c r="J30" s="176"/>
+      <c r="K30" s="177"/>
     </row>
     <row r="31" spans="2:11">
       <c r="B31" s="71" t="s">
@@ -74657,19 +74659,19 @@
         <f>'Account Overview'!E12</f>
         <v>0</v>
       </c>
-      <c r="G31" s="131" t="s">
+      <c r="G31" s="130" t="s">
         <v>43</v>
       </c>
-      <c r="H31" s="132" t="s">
+      <c r="H31" s="131" t="s">
         <v>44</v>
       </c>
-      <c r="I31" s="133" t="s">
+      <c r="I31" s="132" t="s">
         <v>45</v>
       </c>
-      <c r="J31" s="134" t="s">
+      <c r="J31" s="133" t="s">
         <v>46</v>
       </c>
-      <c r="K31" s="135" t="s">
+      <c r="K31" s="134" t="s">
         <v>47</v>
       </c>
     </row>
@@ -74685,18 +74687,18 @@
       </c>
       <c r="E32" s="77">
         <f ca="1">DATEDIF(C31,C33,"d")/7</f>
-        <v>46.285714285714285</v>
+        <v>46.428571428571431</v>
       </c>
       <c r="G32" s="75" t="s">
         <v>50</v>
       </c>
-      <c r="H32" s="124"/>
-      <c r="I32" s="124"/>
-      <c r="J32" s="126">
+      <c r="H32" s="123"/>
+      <c r="I32" s="123"/>
+      <c r="J32" s="125">
         <f t="shared" ref="J32:J38" si="2">H32-I32</f>
         <v>0</v>
       </c>
-      <c r="K32" s="127">
+      <c r="K32" s="126">
         <v>0</v>
       </c>
     </row>
@@ -74706,7 +74708,7 @@
       </c>
       <c r="C33" s="79">
         <f ca="1">TODAY()</f>
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="D33" s="70" t="s">
         <v>52</v>
@@ -74718,21 +74720,21 @@
       <c r="G33" s="75" t="s">
         <v>53</v>
       </c>
-      <c r="H33" s="124"/>
-      <c r="I33" s="124"/>
-      <c r="J33" s="126">
+      <c r="H33" s="123"/>
+      <c r="I33" s="123"/>
+      <c r="J33" s="125">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K33" s="127">
+      <c r="K33" s="126">
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:11">
-      <c r="B34" s="170" t="s">
+      <c r="B34" s="169" t="s">
         <v>54</v>
       </c>
-      <c r="C34" s="171"/>
+      <c r="C34" s="170"/>
       <c r="D34" s="73" t="s">
         <v>55</v>
       </c>
@@ -74743,19 +74745,19 @@
       <c r="G34" s="75" t="s">
         <v>56</v>
       </c>
-      <c r="H34" s="125"/>
-      <c r="I34" s="124"/>
-      <c r="J34" s="126">
+      <c r="H34" s="124"/>
+      <c r="I34" s="123"/>
+      <c r="J34" s="125">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K34" s="127">
+      <c r="K34" s="126">
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:11">
-      <c r="B35" s="172"/>
-      <c r="C35" s="173"/>
+      <c r="B35" s="171"/>
+      <c r="C35" s="172"/>
       <c r="D35" s="69" t="s">
         <v>57</v>
       </c>
@@ -74766,19 +74768,19 @@
       <c r="G35" s="75" t="s">
         <v>58</v>
       </c>
-      <c r="H35" s="125"/>
-      <c r="I35" s="124"/>
-      <c r="J35" s="126">
+      <c r="H35" s="124"/>
+      <c r="I35" s="123"/>
+      <c r="J35" s="125">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K35" s="127">
+      <c r="K35" s="126">
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:11" ht="17" thickBot="1">
-      <c r="B36" s="174"/>
-      <c r="C36" s="175"/>
+      <c r="B36" s="173"/>
+      <c r="C36" s="174"/>
       <c r="D36" s="81" t="s">
         <v>52</v>
       </c>
@@ -74789,13 +74791,13 @@
       <c r="G36" s="75" t="s">
         <v>59</v>
       </c>
-      <c r="H36" s="125"/>
-      <c r="I36" s="124"/>
-      <c r="J36" s="126">
+      <c r="H36" s="124"/>
+      <c r="I36" s="123"/>
+      <c r="J36" s="125">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K36" s="127">
+      <c r="K36" s="126">
         <v>0</v>
       </c>
     </row>
@@ -74803,13 +74805,13 @@
       <c r="G37" s="75" t="s">
         <v>60</v>
       </c>
-      <c r="H37" s="124"/>
-      <c r="I37" s="124"/>
-      <c r="J37" s="126">
+      <c r="H37" s="123"/>
+      <c r="I37" s="123"/>
+      <c r="J37" s="125">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K37" s="127">
+      <c r="K37" s="126">
         <v>0</v>
       </c>
     </row>
@@ -74817,33 +74819,33 @@
       <c r="G38" s="75" t="s">
         <v>61</v>
       </c>
-      <c r="H38" s="124"/>
-      <c r="I38" s="124"/>
-      <c r="J38" s="126">
+      <c r="H38" s="123"/>
+      <c r="I38" s="123"/>
+      <c r="J38" s="125">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K38" s="127">
+      <c r="K38" s="126">
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="2:11" ht="17" thickBot="1">
-      <c r="G39" s="129" t="s">
+      <c r="G39" s="128" t="s">
         <v>62</v>
       </c>
-      <c r="H39" s="130">
+      <c r="H39" s="129">
         <f>SUM(H32:H38)</f>
         <v>0</v>
       </c>
-      <c r="I39" s="130">
+      <c r="I39" s="129">
         <f>SUM(I32:I38)</f>
         <v>0</v>
       </c>
-      <c r="J39" s="130">
+      <c r="J39" s="129">
         <f>SUM(J32:J38)</f>
         <v>0</v>
       </c>
-      <c r="K39" s="128">
+      <c r="K39" s="127">
         <v>0</v>
       </c>
     </row>
@@ -74923,7 +74925,7 @@
       </c>
       <c r="E3" s="12">
         <f ca="1">TODAY()</f>
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="F3" s="6"/>
       <c r="G3" s="13" t="s">
@@ -74971,12 +74973,12 @@
       </c>
     </row>
     <row r="6" spans="2:9" ht="19" thickBot="1">
-      <c r="B6" s="185" t="s">
+      <c r="B6" s="184" t="s">
         <v>81</v>
       </c>
-      <c r="C6" s="185"/>
-      <c r="D6" s="185"/>
-      <c r="E6" s="185"/>
+      <c r="C6" s="184"/>
+      <c r="D6" s="184"/>
+      <c r="E6" s="184"/>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
@@ -75011,12 +75013,12 @@
       <c r="I8" s="8"/>
     </row>
     <row r="9" spans="2:9" ht="19" thickBot="1">
-      <c r="B9" s="185" t="s">
+      <c r="B9" s="184" t="s">
         <v>85</v>
       </c>
-      <c r="C9" s="185"/>
-      <c r="D9" s="185"/>
-      <c r="E9" s="185"/>
+      <c r="C9" s="184"/>
+      <c r="D9" s="184"/>
+      <c r="E9" s="184"/>
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
@@ -75132,12 +75134,12 @@
       <c r="I17" s="8"/>
     </row>
     <row r="18" spans="2:9" ht="19" thickBot="1">
-      <c r="B18" s="185" t="s">
+      <c r="B18" s="184" t="s">
         <v>97</v>
       </c>
-      <c r="C18" s="185"/>
-      <c r="D18" s="185"/>
-      <c r="E18" s="185"/>
+      <c r="C18" s="184"/>
+      <c r="D18" s="184"/>
+      <c r="E18" s="184"/>
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
       <c r="H18" s="8"/>
@@ -75150,10 +75152,10 @@
       <c r="C19" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="D19" s="186" t="s">
+      <c r="D19" s="185" t="s">
         <v>99</v>
       </c>
-      <c r="E19" s="187"/>
+      <c r="E19" s="186"/>
       <c r="F19" s="8"/>
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
@@ -75166,10 +75168,10 @@
       <c r="C20" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="D20" s="188" t="s">
+      <c r="D20" s="187" t="s">
         <v>101</v>
       </c>
-      <c r="E20" s="189"/>
+      <c r="E20" s="188"/>
     </row>
     <row r="21" spans="2:9" ht="43" customHeight="1" thickBot="1">
       <c r="B21" s="33" t="s">
@@ -75178,10 +75180,10 @@
       <c r="C21" s="41" t="s">
         <v>77</v>
       </c>
-      <c r="D21" s="183" t="s">
+      <c r="D21" s="182" t="s">
         <v>103</v>
       </c>
-      <c r="E21" s="184"/>
+      <c r="E21" s="183"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -75204,75 +75206,75 @@
   <dimension ref="B1:J24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="3.83203125" style="103" customWidth="1"/>
-    <col min="2" max="2" width="18.5" style="103" customWidth="1"/>
-    <col min="3" max="3" width="28.1640625" style="103" customWidth="1"/>
-    <col min="4" max="4" width="20.6640625" style="103" customWidth="1"/>
-    <col min="5" max="5" width="43" style="103" customWidth="1"/>
-    <col min="6" max="6" width="3.6640625" style="103" customWidth="1"/>
-    <col min="7" max="7" width="21.1640625" style="103" customWidth="1"/>
-    <col min="8" max="8" width="4.1640625" style="103" customWidth="1"/>
-    <col min="9" max="9" width="21.1640625" style="103" customWidth="1"/>
-    <col min="10" max="16384" width="11" style="103"/>
+    <col min="1" max="1" width="3.83203125" style="102" customWidth="1"/>
+    <col min="2" max="2" width="18.5" style="102" customWidth="1"/>
+    <col min="3" max="3" width="28.1640625" style="102" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" style="102" customWidth="1"/>
+    <col min="5" max="5" width="43" style="102" customWidth="1"/>
+    <col min="6" max="6" width="3.6640625" style="102" customWidth="1"/>
+    <col min="7" max="7" width="21.1640625" style="102" customWidth="1"/>
+    <col min="8" max="8" width="4.1640625" style="102" customWidth="1"/>
+    <col min="9" max="9" width="21.1640625" style="102" customWidth="1"/>
+    <col min="10" max="16384" width="11" style="102"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" s="62" customFormat="1" ht="8" customHeight="1">
       <c r="C1" s="63"/>
       <c r="I1" s="67"/>
-      <c r="J1" s="99"/>
+      <c r="J1" s="98"/>
     </row>
     <row r="2" spans="2:10" s="62" customFormat="1" ht="15" customHeight="1">
-      <c r="B2" s="194" t="s">
+      <c r="B2" s="195" t="s">
         <v>104</v>
       </c>
-      <c r="C2" s="194"/>
-      <c r="D2" s="194"/>
-      <c r="E2" s="194"/>
-      <c r="F2" s="194"/>
-      <c r="G2" s="194"/>
-      <c r="H2" s="194"/>
-      <c r="I2" s="194"/>
-      <c r="J2" s="99"/>
+      <c r="C2" s="195"/>
+      <c r="D2" s="195"/>
+      <c r="E2" s="195"/>
+      <c r="F2" s="195"/>
+      <c r="G2" s="195"/>
+      <c r="H2" s="195"/>
+      <c r="I2" s="195"/>
+      <c r="J2" s="98"/>
     </row>
     <row r="3" spans="2:10" s="62" customFormat="1" ht="15" customHeight="1">
-      <c r="B3" s="194"/>
-      <c r="C3" s="194"/>
-      <c r="D3" s="194"/>
-      <c r="E3" s="194"/>
-      <c r="F3" s="194"/>
-      <c r="G3" s="194"/>
-      <c r="H3" s="194"/>
-      <c r="I3" s="194"/>
-      <c r="J3" s="99"/>
+      <c r="B3" s="195"/>
+      <c r="C3" s="195"/>
+      <c r="D3" s="195"/>
+      <c r="E3" s="195"/>
+      <c r="F3" s="195"/>
+      <c r="G3" s="195"/>
+      <c r="H3" s="195"/>
+      <c r="I3" s="195"/>
+      <c r="J3" s="98"/>
     </row>
     <row r="4" spans="2:10" s="62" customFormat="1" ht="12" customHeight="1">
-      <c r="B4" s="100"/>
-      <c r="C4" s="100"/>
-      <c r="D4" s="100"/>
-      <c r="E4" s="100"/>
-      <c r="F4" s="100"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="100"/>
-      <c r="I4" s="113"/>
-      <c r="J4" s="99"/>
+      <c r="B4" s="99"/>
+      <c r="C4" s="99"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="99"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="99"/>
+      <c r="H4" s="99"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="98"/>
     </row>
     <row r="5" spans="2:10" s="62" customFormat="1">
-      <c r="B5" s="101" t="s">
+      <c r="B5" s="100" t="s">
         <v>105</v>
       </c>
       <c r="D5" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="102">
+      <c r="E5" s="101">
         <f>'Account Overview'!I5</f>
         <v>0</v>
       </c>
-      <c r="H5" s="211"/>
-      <c r="I5" s="211"/>
-      <c r="J5" s="99"/>
+      <c r="H5" s="210"/>
+      <c r="I5" s="210"/>
+      <c r="J5" s="98"/>
     </row>
     <row r="6" spans="2:10" s="62" customFormat="1">
-      <c r="B6" s="101" t="s">
+      <c r="B6" s="100" t="s">
         <v>23</v>
       </c>
       <c r="C6" s="62">
@@ -75282,233 +75284,234 @@
       <c r="D6" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="98">
+      <c r="E6" s="97">
         <f ca="1">TODAY()</f>
-        <v>46142</v>
+        <v>46143</v>
       </c>
-      <c r="H6" s="211"/>
-      <c r="I6" s="211"/>
-      <c r="J6" s="99"/>
+      <c r="H6" s="210"/>
+      <c r="I6" s="210"/>
+      <c r="J6" s="98"/>
     </row>
     <row r="7" spans="2:10" s="62" customFormat="1" ht="10" customHeight="1">
       <c r="C7" s="63"/>
-      <c r="H7" s="211"/>
-      <c r="I7" s="211"/>
-      <c r="J7" s="99"/>
+      <c r="H7" s="210"/>
+      <c r="I7" s="210"/>
+      <c r="J7" s="98"/>
     </row>
     <row r="8" spans="2:10" ht="30" customHeight="1" thickBot="1">
-      <c r="B8" s="208" t="s">
+      <c r="B8" s="207" t="s">
         <v>106</v>
       </c>
-      <c r="C8" s="208"/>
-      <c r="D8" s="208"/>
-      <c r="E8" s="208"/>
-      <c r="F8" s="208"/>
-      <c r="G8" s="208"/>
-      <c r="H8" s="212"/>
-      <c r="I8" s="212"/>
+      <c r="C8" s="207"/>
+      <c r="D8" s="207"/>
+      <c r="E8" s="207"/>
+      <c r="F8" s="207"/>
+      <c r="G8" s="207"/>
+      <c r="H8" s="211"/>
+      <c r="I8" s="211"/>
     </row>
     <row r="9" spans="2:10" ht="55" customHeight="1">
-      <c r="B9" s="114" t="s">
+      <c r="B9" s="113" t="s">
         <v>107</v>
       </c>
-      <c r="C9" s="104" t="s">
+      <c r="C9" s="103" t="s">
         <v>79</v>
       </c>
-      <c r="D9" s="209" t="s">
+      <c r="D9" s="208" t="s">
         <v>108</v>
       </c>
-      <c r="E9" s="209"/>
-      <c r="F9" s="209"/>
-      <c r="G9" s="209"/>
-      <c r="H9" s="209"/>
-      <c r="I9" s="210"/>
+      <c r="E9" s="208"/>
+      <c r="F9" s="208"/>
+      <c r="G9" s="208"/>
+      <c r="H9" s="208"/>
+      <c r="I9" s="209"/>
     </row>
     <row r="10" spans="2:10" ht="15" customHeight="1"/>
     <row r="11" spans="2:10" ht="30" customHeight="1" thickBot="1">
-      <c r="B11" s="208" t="s">
+      <c r="B11" s="207" t="s">
         <v>109</v>
       </c>
-      <c r="C11" s="208"/>
-      <c r="D11" s="208"/>
-      <c r="E11" s="208"/>
+      <c r="C11" s="207"/>
+      <c r="D11" s="207"/>
+      <c r="E11" s="207"/>
     </row>
     <row r="12" spans="2:10" ht="25" customHeight="1">
-      <c r="B12" s="116" t="s">
+      <c r="B12" s="115" t="s">
         <v>110</v>
       </c>
-      <c r="C12" s="117" t="s">
+      <c r="C12" s="116" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="196" t="s">
+      <c r="D12" s="197" t="s">
         <v>15</v>
       </c>
-      <c r="E12" s="197"/>
-      <c r="G12" s="123" t="s">
+      <c r="E12" s="198"/>
+      <c r="G12" s="122" t="s">
         <v>111</v>
       </c>
-      <c r="I12" s="123" t="s">
+      <c r="I12" s="122" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="13" spans="2:10" ht="55" customHeight="1">
-      <c r="B13" s="115" t="s">
+      <c r="B13" s="114" t="s">
         <v>113</v>
       </c>
-      <c r="C13" s="105" t="s">
+      <c r="C13" s="104" t="s">
         <v>80</v>
       </c>
-      <c r="D13" s="204" t="s">
+      <c r="D13" s="189" t="s">
         <v>114</v>
       </c>
-      <c r="E13" s="205"/>
-      <c r="G13" s="110" t="s">
+      <c r="E13" s="190"/>
+      <c r="G13" s="109" t="s">
         <v>79</v>
       </c>
-      <c r="I13" s="110" t="s">
+      <c r="I13" s="109" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="14" spans="2:10" ht="55" customHeight="1">
-      <c r="B14" s="118" t="s">
+      <c r="B14" s="117" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="105" t="s">
+      <c r="C14" s="104" t="s">
         <v>77</v>
       </c>
-      <c r="D14" s="202" t="s">
+      <c r="D14" s="203" t="s">
         <v>115</v>
       </c>
-      <c r="E14" s="203"/>
-      <c r="G14" s="111" t="s">
+      <c r="E14" s="204"/>
+      <c r="G14" s="110" t="s">
         <v>77</v>
       </c>
-      <c r="I14" s="111" t="s">
+      <c r="I14" s="110" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="15" spans="2:10" ht="55" customHeight="1" thickBot="1">
-      <c r="B15" s="115" t="s">
+      <c r="B15" s="114" t="s">
         <v>116</v>
       </c>
-      <c r="C15" s="105" t="s">
+      <c r="C15" s="104" t="s">
         <v>79</v>
       </c>
-      <c r="D15" s="204" t="s">
+      <c r="D15" s="189" t="s">
         <v>117</v>
       </c>
-      <c r="E15" s="205"/>
-      <c r="F15" s="107"/>
-      <c r="G15" s="112" t="s">
+      <c r="E15" s="190"/>
+      <c r="F15" s="106"/>
+      <c r="G15" s="111" t="s">
         <v>72</v>
       </c>
-      <c r="I15" s="112" t="s">
+      <c r="I15" s="111" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="16" spans="2:10" ht="55" customHeight="1">
-      <c r="B16" s="118" t="s">
+      <c r="B16" s="117" t="s">
         <v>118</v>
       </c>
-      <c r="C16" s="105" t="s">
+      <c r="C16" s="104" t="s">
         <v>77</v>
       </c>
-      <c r="D16" s="202" t="s">
+      <c r="D16" s="203" t="s">
         <v>119</v>
       </c>
-      <c r="E16" s="203"/>
-      <c r="F16" s="108"/>
-      <c r="H16" s="108"/>
+      <c r="E16" s="204"/>
+      <c r="F16" s="107"/>
+      <c r="H16" s="107"/>
     </row>
     <row r="17" spans="2:8" ht="55" customHeight="1">
-      <c r="B17" s="115" t="s">
+      <c r="B17" s="114" t="s">
         <v>120</v>
       </c>
-      <c r="C17" s="105" t="s">
+      <c r="C17" s="104" t="s">
         <v>77</v>
       </c>
-      <c r="D17" s="206" t="s">
+      <c r="D17" s="205" t="s">
         <v>121</v>
       </c>
-      <c r="E17" s="207"/>
-      <c r="F17" s="108"/>
-      <c r="H17" s="108"/>
+      <c r="E17" s="206"/>
+      <c r="F17" s="107"/>
+      <c r="H17" s="107"/>
     </row>
     <row r="18" spans="2:8" ht="55" customHeight="1" thickBot="1">
-      <c r="B18" s="119" t="s">
+      <c r="B18" s="118" t="s">
         <v>122</v>
       </c>
-      <c r="C18" s="109" t="s">
+      <c r="C18" s="108" t="s">
         <v>72</v>
       </c>
-      <c r="D18" s="200" t="s">
+      <c r="D18" s="201" t="s">
         <v>123</v>
       </c>
-      <c r="E18" s="201"/>
-      <c r="F18" s="108"/>
-      <c r="H18" s="108"/>
+      <c r="E18" s="202"/>
+      <c r="F18" s="107"/>
+      <c r="H18" s="107"/>
     </row>
     <row r="19" spans="2:8" ht="18" customHeight="1">
-      <c r="E19" s="106"/>
+      <c r="E19" s="105"/>
     </row>
     <row r="20" spans="2:8" ht="30" customHeight="1" thickBot="1">
-      <c r="B20" s="195" t="s">
+      <c r="B20" s="196" t="s">
         <v>124</v>
       </c>
-      <c r="C20" s="195"/>
-      <c r="D20" s="195"/>
-      <c r="E20" s="195"/>
+      <c r="C20" s="196"/>
+      <c r="D20" s="196"/>
+      <c r="E20" s="196"/>
     </row>
     <row r="21" spans="2:8" ht="25" customHeight="1">
-      <c r="B21" s="116" t="s">
+      <c r="B21" s="115" t="s">
         <v>125</v>
       </c>
-      <c r="C21" s="117" t="s">
+      <c r="C21" s="116" t="s">
         <v>18</v>
       </c>
-      <c r="D21" s="196" t="s">
+      <c r="D21" s="197" t="s">
         <v>126</v>
       </c>
-      <c r="E21" s="197"/>
+      <c r="E21" s="198"/>
     </row>
     <row r="22" spans="2:8" ht="58" customHeight="1">
-      <c r="B22" s="122" t="s">
+      <c r="B22" s="121" t="s">
         <v>127</v>
       </c>
-      <c r="C22" s="105" t="s">
+      <c r="C22" s="104" t="s">
         <v>79</v>
       </c>
-      <c r="D22" s="198" t="s">
+      <c r="D22" s="199" t="s">
         <v>128</v>
       </c>
-      <c r="E22" s="199"/>
+      <c r="E22" s="200"/>
     </row>
     <row r="23" spans="2:8" ht="58" customHeight="1">
-      <c r="B23" s="121" t="s">
+      <c r="B23" s="120" t="s">
         <v>129</v>
       </c>
-      <c r="C23" s="105" t="s">
+      <c r="C23" s="104" t="s">
         <v>72</v>
       </c>
-      <c r="D23" s="190" t="s">
+      <c r="D23" s="191" t="s">
         <v>130</v>
       </c>
-      <c r="E23" s="191"/>
+      <c r="E23" s="192"/>
     </row>
     <row r="24" spans="2:8" ht="58" customHeight="1" thickBot="1">
-      <c r="B24" s="120" t="s">
+      <c r="B24" s="119" t="s">
         <v>131</v>
       </c>
-      <c r="C24" s="109" t="s">
+      <c r="C24" s="108" t="s">
         <v>79</v>
       </c>
-      <c r="D24" s="192" t="s">
+      <c r="D24" s="193" t="s">
         <v>132</v>
       </c>
-      <c r="E24" s="193"/>
+      <c r="E24" s="194"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="D12:E12"/>
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="D23:E23"/>
     <mergeCell ref="D24:E24"/>
@@ -75525,7 +75528,6 @@
     <mergeCell ref="D9:I9"/>
     <mergeCell ref="H5:I8"/>
     <mergeCell ref="B8:G8"/>
-    <mergeCell ref="D12:E12"/>
   </mergeCells>
   <conditionalFormatting sqref="C9 C13:C18 C22:C24">
     <cfRule type="containsText" dxfId="24" priority="5" operator="containsText" text="At Risk">
@@ -75572,75 +75574,75 @@
   <dimension ref="B1:J24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="3.83203125" style="103" customWidth="1"/>
-    <col min="2" max="2" width="18.5" style="103" customWidth="1"/>
-    <col min="3" max="3" width="28.1640625" style="103" customWidth="1"/>
-    <col min="4" max="4" width="20.6640625" style="103" customWidth="1"/>
-    <col min="5" max="5" width="43" style="103" customWidth="1"/>
-    <col min="6" max="6" width="3.6640625" style="103" customWidth="1"/>
-    <col min="7" max="7" width="21.1640625" style="103" customWidth="1"/>
-    <col min="8" max="8" width="4.1640625" style="103" customWidth="1"/>
-    <col min="9" max="9" width="21.1640625" style="103" customWidth="1"/>
-    <col min="10" max="16384" width="11" style="103"/>
+    <col min="1" max="1" width="3.83203125" style="102" customWidth="1"/>
+    <col min="2" max="2" width="18.5" style="102" customWidth="1"/>
+    <col min="3" max="3" width="28.1640625" style="102" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" style="102" customWidth="1"/>
+    <col min="5" max="5" width="43" style="102" customWidth="1"/>
+    <col min="6" max="6" width="3.6640625" style="102" customWidth="1"/>
+    <col min="7" max="7" width="21.1640625" style="102" customWidth="1"/>
+    <col min="8" max="8" width="4.1640625" style="102" customWidth="1"/>
+    <col min="9" max="9" width="21.1640625" style="102" customWidth="1"/>
+    <col min="10" max="16384" width="11" style="102"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" s="62" customFormat="1" ht="8" customHeight="1">
       <c r="C1" s="63"/>
       <c r="I1" s="67"/>
-      <c r="J1" s="99"/>
+      <c r="J1" s="98"/>
     </row>
     <row r="2" spans="2:10" s="62" customFormat="1" ht="15" customHeight="1">
-      <c r="B2" s="194" t="s">
+      <c r="B2" s="195" t="s">
         <v>104</v>
       </c>
-      <c r="C2" s="194"/>
-      <c r="D2" s="194"/>
-      <c r="E2" s="194"/>
-      <c r="F2" s="194"/>
-      <c r="G2" s="194"/>
-      <c r="H2" s="194"/>
-      <c r="I2" s="194"/>
-      <c r="J2" s="99"/>
+      <c r="C2" s="195"/>
+      <c r="D2" s="195"/>
+      <c r="E2" s="195"/>
+      <c r="F2" s="195"/>
+      <c r="G2" s="195"/>
+      <c r="H2" s="195"/>
+      <c r="I2" s="195"/>
+      <c r="J2" s="98"/>
     </row>
     <row r="3" spans="2:10" s="62" customFormat="1" ht="15" customHeight="1">
-      <c r="B3" s="194"/>
-      <c r="C3" s="194"/>
-      <c r="D3" s="194"/>
-      <c r="E3" s="194"/>
-      <c r="F3" s="194"/>
-      <c r="G3" s="194"/>
-      <c r="H3" s="194"/>
-      <c r="I3" s="194"/>
-      <c r="J3" s="99"/>
+      <c r="B3" s="195"/>
+      <c r="C3" s="195"/>
+      <c r="D3" s="195"/>
+      <c r="E3" s="195"/>
+      <c r="F3" s="195"/>
+      <c r="G3" s="195"/>
+      <c r="H3" s="195"/>
+      <c r="I3" s="195"/>
+      <c r="J3" s="98"/>
     </row>
     <row r="4" spans="2:10" s="62" customFormat="1" ht="12" customHeight="1">
-      <c r="B4" s="100"/>
-      <c r="C4" s="100"/>
-      <c r="D4" s="100"/>
-      <c r="E4" s="100"/>
-      <c r="F4" s="100"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="100"/>
-      <c r="I4" s="113"/>
-      <c r="J4" s="99"/>
+      <c r="B4" s="99"/>
+      <c r="C4" s="99"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="99"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="99"/>
+      <c r="H4" s="99"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="98"/>
     </row>
     <row r="5" spans="2:10" s="62" customFormat="1">
-      <c r="B5" s="101" t="s">
+      <c r="B5" s="100" t="s">
         <v>105</v>
       </c>
       <c r="D5" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="102">
+      <c r="E5" s="101">
         <f>'Account Overview'!I5</f>
         <v>0</v>
       </c>
-      <c r="H5" s="211"/>
-      <c r="I5" s="211"/>
-      <c r="J5" s="99"/>
+      <c r="H5" s="210"/>
+      <c r="I5" s="210"/>
+      <c r="J5" s="98"/>
     </row>
     <row r="6" spans="2:10" s="62" customFormat="1">
-      <c r="B6" s="101" t="s">
+      <c r="B6" s="100" t="s">
         <v>23</v>
       </c>
       <c r="C6" s="62">
@@ -75650,238 +75652,233 @@
       <c r="D6" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="98">
+      <c r="E6" s="97">
         <f ca="1">TODAY()</f>
-        <v>46142</v>
+        <v>46143</v>
       </c>
-      <c r="H6" s="211"/>
-      <c r="I6" s="211"/>
-      <c r="J6" s="99"/>
+      <c r="H6" s="210"/>
+      <c r="I6" s="210"/>
+      <c r="J6" s="98"/>
     </row>
     <row r="7" spans="2:10" s="62" customFormat="1" ht="10" customHeight="1">
       <c r="C7" s="63"/>
-      <c r="H7" s="211"/>
-      <c r="I7" s="211"/>
-      <c r="J7" s="99"/>
+      <c r="H7" s="210"/>
+      <c r="I7" s="210"/>
+      <c r="J7" s="98"/>
     </row>
     <row r="8" spans="2:10" ht="30" customHeight="1" thickBot="1">
-      <c r="B8" s="208" t="s">
+      <c r="B8" s="207" t="s">
         <v>106</v>
       </c>
-      <c r="C8" s="208"/>
-      <c r="D8" s="208"/>
-      <c r="E8" s="208"/>
-      <c r="F8" s="208"/>
-      <c r="G8" s="208"/>
-      <c r="H8" s="212"/>
-      <c r="I8" s="212"/>
+      <c r="C8" s="207"/>
+      <c r="D8" s="207"/>
+      <c r="E8" s="207"/>
+      <c r="F8" s="207"/>
+      <c r="G8" s="207"/>
+      <c r="H8" s="211"/>
+      <c r="I8" s="211"/>
     </row>
     <row r="9" spans="2:10" ht="55" customHeight="1">
-      <c r="B9" s="114" t="s">
+      <c r="B9" s="113" t="s">
         <v>107</v>
       </c>
-      <c r="C9" s="104" t="s">
+      <c r="C9" s="103" t="s">
         <v>77</v>
       </c>
-      <c r="D9" s="209" t="s">
+      <c r="D9" s="208" t="s">
         <v>108</v>
       </c>
-      <c r="E9" s="209"/>
-      <c r="F9" s="209"/>
-      <c r="G9" s="209"/>
-      <c r="H9" s="209"/>
-      <c r="I9" s="210"/>
+      <c r="E9" s="208"/>
+      <c r="F9" s="208"/>
+      <c r="G9" s="208"/>
+      <c r="H9" s="208"/>
+      <c r="I9" s="209"/>
     </row>
     <row r="10" spans="2:10" ht="15" customHeight="1"/>
     <row r="11" spans="2:10" ht="30" customHeight="1" thickBot="1">
-      <c r="B11" s="208" t="s">
+      <c r="B11" s="207" t="s">
         <v>109</v>
       </c>
-      <c r="C11" s="208"/>
-      <c r="D11" s="208"/>
-      <c r="E11" s="208"/>
+      <c r="C11" s="207"/>
+      <c r="D11" s="207"/>
+      <c r="E11" s="207"/>
     </row>
     <row r="12" spans="2:10" ht="25" customHeight="1">
-      <c r="B12" s="116" t="s">
+      <c r="B12" s="115" t="s">
         <v>110</v>
       </c>
-      <c r="C12" s="117" t="s">
+      <c r="C12" s="116" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="196" t="s">
+      <c r="D12" s="197" t="s">
         <v>15</v>
       </c>
-      <c r="E12" s="197"/>
-      <c r="G12" s="123" t="s">
+      <c r="E12" s="198"/>
+      <c r="G12" s="122" t="s">
         <v>111</v>
       </c>
-      <c r="I12" s="123" t="s">
+      <c r="I12" s="122" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="13" spans="2:10" ht="55" customHeight="1">
-      <c r="B13" s="115" t="s">
+      <c r="B13" s="114" t="s">
         <v>113</v>
       </c>
-      <c r="C13" s="105" t="s">
+      <c r="C13" s="104" t="s">
         <v>80</v>
       </c>
-      <c r="D13" s="204" t="s">
+      <c r="D13" s="189" t="s">
         <v>133</v>
       </c>
-      <c r="E13" s="205"/>
-      <c r="G13" s="110" t="s">
+      <c r="E13" s="190"/>
+      <c r="G13" s="109" t="s">
         <v>79</v>
       </c>
-      <c r="I13" s="110" t="s">
+      <c r="I13" s="109" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="14" spans="2:10" ht="55" customHeight="1">
-      <c r="B14" s="118" t="s">
+      <c r="B14" s="117" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="105" t="s">
+      <c r="C14" s="104" t="s">
         <v>77</v>
       </c>
-      <c r="D14" s="202" t="s">
+      <c r="D14" s="203" t="s">
         <v>115</v>
       </c>
-      <c r="E14" s="203"/>
-      <c r="G14" s="111" t="s">
+      <c r="E14" s="204"/>
+      <c r="G14" s="110" t="s">
         <v>77</v>
       </c>
-      <c r="I14" s="111" t="s">
+      <c r="I14" s="110" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="15" spans="2:10" ht="55" customHeight="1" thickBot="1">
-      <c r="B15" s="115" t="s">
+      <c r="B15" s="114" t="s">
         <v>116</v>
       </c>
-      <c r="C15" s="105" t="s">
+      <c r="C15" s="104" t="s">
         <v>79</v>
       </c>
-      <c r="D15" s="204" t="s">
+      <c r="D15" s="189" t="s">
         <v>117</v>
       </c>
-      <c r="E15" s="205"/>
-      <c r="F15" s="107"/>
-      <c r="G15" s="112" t="s">
+      <c r="E15" s="190"/>
+      <c r="F15" s="106"/>
+      <c r="G15" s="111" t="s">
         <v>72</v>
       </c>
-      <c r="I15" s="112" t="s">
+      <c r="I15" s="111" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="16" spans="2:10" ht="55" customHeight="1">
-      <c r="B16" s="118" t="s">
+      <c r="B16" s="117" t="s">
         <v>118</v>
       </c>
-      <c r="C16" s="105" t="s">
+      <c r="C16" s="104" t="s">
         <v>77</v>
       </c>
-      <c r="D16" s="202" t="s">
+      <c r="D16" s="203" t="s">
         <v>119</v>
       </c>
-      <c r="E16" s="203"/>
-      <c r="F16" s="108"/>
-      <c r="H16" s="108"/>
+      <c r="E16" s="204"/>
+      <c r="F16" s="107"/>
+      <c r="H16" s="107"/>
     </row>
     <row r="17" spans="2:8" ht="55" customHeight="1">
-      <c r="B17" s="115" t="s">
+      <c r="B17" s="114" t="s">
         <v>120</v>
       </c>
-      <c r="C17" s="105" t="s">
+      <c r="C17" s="104" t="s">
         <v>77</v>
       </c>
-      <c r="D17" s="206" t="s">
+      <c r="D17" s="205" t="s">
         <v>121</v>
       </c>
-      <c r="E17" s="207"/>
-      <c r="F17" s="108"/>
-      <c r="H17" s="108"/>
+      <c r="E17" s="206"/>
+      <c r="F17" s="107"/>
+      <c r="H17" s="107"/>
     </row>
     <row r="18" spans="2:8" ht="55" customHeight="1" thickBot="1">
-      <c r="B18" s="119" t="s">
+      <c r="B18" s="118" t="s">
         <v>122</v>
       </c>
-      <c r="C18" s="109" t="s">
+      <c r="C18" s="108" t="s">
         <v>72</v>
       </c>
-      <c r="D18" s="200" t="s">
+      <c r="D18" s="201" t="s">
         <v>123</v>
       </c>
-      <c r="E18" s="201"/>
-      <c r="F18" s="108"/>
-      <c r="H18" s="108"/>
+      <c r="E18" s="202"/>
+      <c r="F18" s="107"/>
+      <c r="H18" s="107"/>
     </row>
     <row r="19" spans="2:8" ht="18" customHeight="1">
-      <c r="E19" s="106"/>
+      <c r="E19" s="105"/>
     </row>
     <row r="20" spans="2:8" ht="30" customHeight="1" thickBot="1">
-      <c r="B20" s="195" t="s">
+      <c r="B20" s="196" t="s">
         <v>124</v>
       </c>
-      <c r="C20" s="195"/>
-      <c r="D20" s="195"/>
-      <c r="E20" s="195"/>
+      <c r="C20" s="196"/>
+      <c r="D20" s="196"/>
+      <c r="E20" s="196"/>
     </row>
     <row r="21" spans="2:8" ht="25" customHeight="1">
-      <c r="B21" s="116" t="s">
+      <c r="B21" s="115" t="s">
         <v>125</v>
       </c>
-      <c r="C21" s="117" t="s">
+      <c r="C21" s="116" t="s">
         <v>18</v>
       </c>
-      <c r="D21" s="196" t="s">
+      <c r="D21" s="197" t="s">
         <v>126</v>
       </c>
-      <c r="E21" s="197"/>
+      <c r="E21" s="198"/>
     </row>
     <row r="22" spans="2:8" ht="58" customHeight="1">
-      <c r="B22" s="122" t="s">
+      <c r="B22" s="121" t="s">
         <v>127</v>
       </c>
-      <c r="C22" s="105" t="s">
+      <c r="C22" s="104" t="s">
         <v>79</v>
       </c>
-      <c r="D22" s="198" t="s">
+      <c r="D22" s="199" t="s">
         <v>128</v>
       </c>
-      <c r="E22" s="199"/>
+      <c r="E22" s="200"/>
     </row>
     <row r="23" spans="2:8" ht="58" customHeight="1">
-      <c r="B23" s="121" t="s">
+      <c r="B23" s="120" t="s">
         <v>129</v>
       </c>
-      <c r="C23" s="105" t="s">
+      <c r="C23" s="104" t="s">
         <v>72</v>
       </c>
-      <c r="D23" s="190" t="s">
+      <c r="D23" s="191" t="s">
         <v>130</v>
       </c>
-      <c r="E23" s="191"/>
+      <c r="E23" s="192"/>
     </row>
     <row r="24" spans="2:8" ht="58" customHeight="1" thickBot="1">
-      <c r="B24" s="120" t="s">
+      <c r="B24" s="119" t="s">
         <v>131</v>
       </c>
-      <c r="C24" s="109" t="s">
+      <c r="C24" s="108" t="s">
         <v>79</v>
       </c>
-      <c r="D24" s="192" t="s">
+      <c r="D24" s="193" t="s">
         <v>132</v>
       </c>
-      <c r="E24" s="193"/>
+      <c r="E24" s="194"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D24:E24"/>
     <mergeCell ref="D17:E17"/>
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="B2:I3"/>
@@ -75894,6 +75891,11 @@
     <mergeCell ref="D14:E14"/>
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="D16:E16"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D24:E24"/>
   </mergeCells>
   <conditionalFormatting sqref="C9 C13:C18 C22:C24">
     <cfRule type="containsText" dxfId="18" priority="5" operator="containsText" text="At Risk">
@@ -75940,75 +75942,75 @@
   <dimension ref="B1:J24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="3.83203125" style="103" customWidth="1"/>
-    <col min="2" max="2" width="18.5" style="103" customWidth="1"/>
-    <col min="3" max="3" width="28.1640625" style="103" customWidth="1"/>
-    <col min="4" max="4" width="20.6640625" style="103" customWidth="1"/>
-    <col min="5" max="5" width="43" style="103" customWidth="1"/>
-    <col min="6" max="6" width="3.6640625" style="103" customWidth="1"/>
-    <col min="7" max="7" width="21.1640625" style="103" customWidth="1"/>
-    <col min="8" max="8" width="4.1640625" style="103" customWidth="1"/>
-    <col min="9" max="9" width="21.1640625" style="103" customWidth="1"/>
-    <col min="10" max="16384" width="11" style="103"/>
+    <col min="1" max="1" width="3.83203125" style="102" customWidth="1"/>
+    <col min="2" max="2" width="18.5" style="102" customWidth="1"/>
+    <col min="3" max="3" width="28.1640625" style="102" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" style="102" customWidth="1"/>
+    <col min="5" max="5" width="43" style="102" customWidth="1"/>
+    <col min="6" max="6" width="3.6640625" style="102" customWidth="1"/>
+    <col min="7" max="7" width="21.1640625" style="102" customWidth="1"/>
+    <col min="8" max="8" width="4.1640625" style="102" customWidth="1"/>
+    <col min="9" max="9" width="21.1640625" style="102" customWidth="1"/>
+    <col min="10" max="16384" width="11" style="102"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" s="62" customFormat="1" ht="8" customHeight="1">
       <c r="C1" s="63"/>
       <c r="I1" s="67"/>
-      <c r="J1" s="99"/>
+      <c r="J1" s="98"/>
     </row>
     <row r="2" spans="2:10" s="62" customFormat="1" ht="15" customHeight="1">
-      <c r="B2" s="194" t="s">
+      <c r="B2" s="195" t="s">
         <v>104</v>
       </c>
-      <c r="C2" s="194"/>
-      <c r="D2" s="194"/>
-      <c r="E2" s="194"/>
-      <c r="F2" s="194"/>
-      <c r="G2" s="194"/>
-      <c r="H2" s="194"/>
-      <c r="I2" s="194"/>
-      <c r="J2" s="99"/>
+      <c r="C2" s="195"/>
+      <c r="D2" s="195"/>
+      <c r="E2" s="195"/>
+      <c r="F2" s="195"/>
+      <c r="G2" s="195"/>
+      <c r="H2" s="195"/>
+      <c r="I2" s="195"/>
+      <c r="J2" s="98"/>
     </row>
     <row r="3" spans="2:10" s="62" customFormat="1" ht="15" customHeight="1">
-      <c r="B3" s="194"/>
-      <c r="C3" s="194"/>
-      <c r="D3" s="194"/>
-      <c r="E3" s="194"/>
-      <c r="F3" s="194"/>
-      <c r="G3" s="194"/>
-      <c r="H3" s="194"/>
-      <c r="I3" s="194"/>
-      <c r="J3" s="99"/>
+      <c r="B3" s="195"/>
+      <c r="C3" s="195"/>
+      <c r="D3" s="195"/>
+      <c r="E3" s="195"/>
+      <c r="F3" s="195"/>
+      <c r="G3" s="195"/>
+      <c r="H3" s="195"/>
+      <c r="I3" s="195"/>
+      <c r="J3" s="98"/>
     </row>
     <row r="4" spans="2:10" s="62" customFormat="1" ht="12" customHeight="1">
-      <c r="B4" s="100"/>
-      <c r="C4" s="100"/>
-      <c r="D4" s="100"/>
-      <c r="E4" s="100"/>
-      <c r="F4" s="100"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="100"/>
-      <c r="I4" s="113"/>
-      <c r="J4" s="99"/>
+      <c r="B4" s="99"/>
+      <c r="C4" s="99"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="99"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="99"/>
+      <c r="H4" s="99"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="98"/>
     </row>
     <row r="5" spans="2:10" s="62" customFormat="1">
-      <c r="B5" s="101" t="s">
+      <c r="B5" s="100" t="s">
         <v>105</v>
       </c>
       <c r="D5" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="102">
+      <c r="E5" s="101">
         <f>'Account Overview'!I5</f>
         <v>0</v>
       </c>
-      <c r="H5" s="211"/>
-      <c r="I5" s="211"/>
-      <c r="J5" s="99"/>
+      <c r="H5" s="210"/>
+      <c r="I5" s="210"/>
+      <c r="J5" s="98"/>
     </row>
     <row r="6" spans="2:10" s="62" customFormat="1">
-      <c r="B6" s="101" t="s">
+      <c r="B6" s="100" t="s">
         <v>23</v>
       </c>
       <c r="C6" s="62">
@@ -76018,238 +76020,233 @@
       <c r="D6" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="98">
+      <c r="E6" s="97">
         <f ca="1">TODAY()</f>
-        <v>46142</v>
+        <v>46143</v>
       </c>
-      <c r="H6" s="211"/>
-      <c r="I6" s="211"/>
-      <c r="J6" s="99"/>
+      <c r="H6" s="210"/>
+      <c r="I6" s="210"/>
+      <c r="J6" s="98"/>
     </row>
     <row r="7" spans="2:10" s="62" customFormat="1" ht="10" customHeight="1">
       <c r="C7" s="63"/>
-      <c r="H7" s="211"/>
-      <c r="I7" s="211"/>
-      <c r="J7" s="99"/>
+      <c r="H7" s="210"/>
+      <c r="I7" s="210"/>
+      <c r="J7" s="98"/>
     </row>
     <row r="8" spans="2:10" ht="30" customHeight="1" thickBot="1">
-      <c r="B8" s="208" t="s">
+      <c r="B8" s="207" t="s">
         <v>106</v>
       </c>
-      <c r="C8" s="208"/>
-      <c r="D8" s="208"/>
-      <c r="E8" s="208"/>
-      <c r="F8" s="208"/>
-      <c r="G8" s="208"/>
-      <c r="H8" s="212"/>
-      <c r="I8" s="212"/>
+      <c r="C8" s="207"/>
+      <c r="D8" s="207"/>
+      <c r="E8" s="207"/>
+      <c r="F8" s="207"/>
+      <c r="G8" s="207"/>
+      <c r="H8" s="211"/>
+      <c r="I8" s="211"/>
     </row>
     <row r="9" spans="2:10" ht="55" customHeight="1">
-      <c r="B9" s="114" t="s">
+      <c r="B9" s="113" t="s">
         <v>107</v>
       </c>
-      <c r="C9" s="104" t="s">
+      <c r="C9" s="103" t="s">
         <v>72</v>
       </c>
-      <c r="D9" s="209" t="s">
+      <c r="D9" s="208" t="s">
         <v>108</v>
       </c>
-      <c r="E9" s="209"/>
-      <c r="F9" s="209"/>
-      <c r="G9" s="209"/>
-      <c r="H9" s="209"/>
-      <c r="I9" s="210"/>
+      <c r="E9" s="208"/>
+      <c r="F9" s="208"/>
+      <c r="G9" s="208"/>
+      <c r="H9" s="208"/>
+      <c r="I9" s="209"/>
     </row>
     <row r="10" spans="2:10" ht="15" customHeight="1"/>
     <row r="11" spans="2:10" ht="30" customHeight="1" thickBot="1">
-      <c r="B11" s="208" t="s">
+      <c r="B11" s="207" t="s">
         <v>109</v>
       </c>
-      <c r="C11" s="208"/>
-      <c r="D11" s="208"/>
-      <c r="E11" s="208"/>
+      <c r="C11" s="207"/>
+      <c r="D11" s="207"/>
+      <c r="E11" s="207"/>
     </row>
     <row r="12" spans="2:10" ht="25" customHeight="1">
-      <c r="B12" s="116" t="s">
+      <c r="B12" s="115" t="s">
         <v>110</v>
       </c>
-      <c r="C12" s="117" t="s">
+      <c r="C12" s="116" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="196" t="s">
+      <c r="D12" s="197" t="s">
         <v>15</v>
       </c>
-      <c r="E12" s="197"/>
-      <c r="G12" s="123" t="s">
+      <c r="E12" s="198"/>
+      <c r="G12" s="122" t="s">
         <v>111</v>
       </c>
-      <c r="I12" s="123" t="s">
+      <c r="I12" s="122" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="13" spans="2:10" ht="55" customHeight="1">
-      <c r="B13" s="115" t="s">
+      <c r="B13" s="114" t="s">
         <v>113</v>
       </c>
-      <c r="C13" s="105" t="s">
+      <c r="C13" s="104" t="s">
         <v>80</v>
       </c>
-      <c r="D13" s="204" t="s">
+      <c r="D13" s="189" t="s">
         <v>133</v>
       </c>
-      <c r="E13" s="205"/>
-      <c r="G13" s="110" t="s">
+      <c r="E13" s="190"/>
+      <c r="G13" s="109" t="s">
         <v>79</v>
       </c>
-      <c r="I13" s="110" t="s">
+      <c r="I13" s="109" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="14" spans="2:10" ht="55" customHeight="1">
-      <c r="B14" s="118" t="s">
+      <c r="B14" s="117" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="105" t="s">
+      <c r="C14" s="104" t="s">
         <v>77</v>
       </c>
-      <c r="D14" s="202" t="s">
+      <c r="D14" s="203" t="s">
         <v>115</v>
       </c>
-      <c r="E14" s="203"/>
-      <c r="G14" s="111" t="s">
+      <c r="E14" s="204"/>
+      <c r="G14" s="110" t="s">
         <v>77</v>
       </c>
-      <c r="I14" s="111" t="s">
+      <c r="I14" s="110" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="15" spans="2:10" ht="55" customHeight="1" thickBot="1">
-      <c r="B15" s="115" t="s">
+      <c r="B15" s="114" t="s">
         <v>116</v>
       </c>
-      <c r="C15" s="105" t="s">
+      <c r="C15" s="104" t="s">
         <v>79</v>
       </c>
-      <c r="D15" s="204" t="s">
+      <c r="D15" s="189" t="s">
         <v>117</v>
       </c>
-      <c r="E15" s="205"/>
-      <c r="F15" s="107"/>
-      <c r="G15" s="112" t="s">
+      <c r="E15" s="190"/>
+      <c r="F15" s="106"/>
+      <c r="G15" s="111" t="s">
         <v>72</v>
       </c>
-      <c r="I15" s="112" t="s">
+      <c r="I15" s="111" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="16" spans="2:10" ht="55" customHeight="1">
-      <c r="B16" s="118" t="s">
+      <c r="B16" s="117" t="s">
         <v>118</v>
       </c>
-      <c r="C16" s="105" t="s">
+      <c r="C16" s="104" t="s">
         <v>77</v>
       </c>
-      <c r="D16" s="202" t="s">
+      <c r="D16" s="203" t="s">
         <v>119</v>
       </c>
-      <c r="E16" s="203"/>
-      <c r="F16" s="108"/>
-      <c r="H16" s="108"/>
+      <c r="E16" s="204"/>
+      <c r="F16" s="107"/>
+      <c r="H16" s="107"/>
     </row>
     <row r="17" spans="2:8" ht="55" customHeight="1">
-      <c r="B17" s="115" t="s">
+      <c r="B17" s="114" t="s">
         <v>120</v>
       </c>
-      <c r="C17" s="105" t="s">
+      <c r="C17" s="104" t="s">
         <v>77</v>
       </c>
-      <c r="D17" s="206" t="s">
+      <c r="D17" s="205" t="s">
         <v>121</v>
       </c>
-      <c r="E17" s="207"/>
-      <c r="F17" s="108"/>
-      <c r="H17" s="108"/>
+      <c r="E17" s="206"/>
+      <c r="F17" s="107"/>
+      <c r="H17" s="107"/>
     </row>
     <row r="18" spans="2:8" ht="55" customHeight="1" thickBot="1">
-      <c r="B18" s="119" t="s">
+      <c r="B18" s="118" t="s">
         <v>122</v>
       </c>
-      <c r="C18" s="109" t="s">
+      <c r="C18" s="108" t="s">
         <v>72</v>
       </c>
-      <c r="D18" s="200" t="s">
+      <c r="D18" s="201" t="s">
         <v>123</v>
       </c>
-      <c r="E18" s="201"/>
-      <c r="F18" s="108"/>
-      <c r="H18" s="108"/>
+      <c r="E18" s="202"/>
+      <c r="F18" s="107"/>
+      <c r="H18" s="107"/>
     </row>
     <row r="19" spans="2:8" ht="18" customHeight="1">
-      <c r="E19" s="106"/>
+      <c r="E19" s="105"/>
     </row>
     <row r="20" spans="2:8" ht="30" customHeight="1" thickBot="1">
-      <c r="B20" s="195" t="s">
+      <c r="B20" s="196" t="s">
         <v>124</v>
       </c>
-      <c r="C20" s="195"/>
-      <c r="D20" s="195"/>
-      <c r="E20" s="195"/>
+      <c r="C20" s="196"/>
+      <c r="D20" s="196"/>
+      <c r="E20" s="196"/>
     </row>
     <row r="21" spans="2:8" ht="25" customHeight="1">
-      <c r="B21" s="116" t="s">
+      <c r="B21" s="115" t="s">
         <v>125</v>
       </c>
-      <c r="C21" s="117" t="s">
+      <c r="C21" s="116" t="s">
         <v>18</v>
       </c>
-      <c r="D21" s="196" t="s">
+      <c r="D21" s="197" t="s">
         <v>126</v>
       </c>
-      <c r="E21" s="197"/>
+      <c r="E21" s="198"/>
     </row>
     <row r="22" spans="2:8" ht="58" customHeight="1">
-      <c r="B22" s="122" t="s">
+      <c r="B22" s="121" t="s">
         <v>127</v>
       </c>
-      <c r="C22" s="105" t="s">
+      <c r="C22" s="104" t="s">
         <v>79</v>
       </c>
-      <c r="D22" s="198" t="s">
+      <c r="D22" s="199" t="s">
         <v>128</v>
       </c>
-      <c r="E22" s="199"/>
+      <c r="E22" s="200"/>
     </row>
     <row r="23" spans="2:8" ht="58" customHeight="1">
-      <c r="B23" s="121" t="s">
+      <c r="B23" s="120" t="s">
         <v>129</v>
       </c>
-      <c r="C23" s="105" t="s">
+      <c r="C23" s="104" t="s">
         <v>72</v>
       </c>
-      <c r="D23" s="190" t="s">
+      <c r="D23" s="191" t="s">
         <v>130</v>
       </c>
-      <c r="E23" s="191"/>
+      <c r="E23" s="192"/>
     </row>
     <row r="24" spans="2:8" ht="58" customHeight="1" thickBot="1">
-      <c r="B24" s="120" t="s">
+      <c r="B24" s="119" t="s">
         <v>131</v>
       </c>
-      <c r="C24" s="109" t="s">
+      <c r="C24" s="108" t="s">
         <v>79</v>
       </c>
-      <c r="D24" s="192" t="s">
+      <c r="D24" s="193" t="s">
         <v>132</v>
       </c>
-      <c r="E24" s="193"/>
+      <c r="E24" s="194"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D24:E24"/>
     <mergeCell ref="D17:E17"/>
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="B2:I3"/>
@@ -76262,6 +76259,11 @@
     <mergeCell ref="D14:E14"/>
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="D16:E16"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D24:E24"/>
   </mergeCells>
   <conditionalFormatting sqref="C9 C13:C18 C22:C24">
     <cfRule type="containsText" dxfId="12" priority="5" operator="containsText" text="At Risk">
@@ -76308,60 +76310,60 @@
   <dimension ref="B1:J24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="3.83203125" style="103" customWidth="1"/>
-    <col min="2" max="2" width="18.5" style="103" customWidth="1"/>
-    <col min="3" max="3" width="28.1640625" style="103" customWidth="1"/>
-    <col min="4" max="4" width="20.6640625" style="103" customWidth="1"/>
-    <col min="5" max="5" width="43" style="103" customWidth="1"/>
-    <col min="6" max="6" width="3.6640625" style="103" customWidth="1"/>
-    <col min="7" max="7" width="21.1640625" style="103" customWidth="1"/>
-    <col min="8" max="8" width="4.1640625" style="103" customWidth="1"/>
-    <col min="9" max="9" width="21.1640625" style="103" customWidth="1"/>
-    <col min="10" max="16384" width="11" style="103"/>
+    <col min="1" max="1" width="3.83203125" style="102" customWidth="1"/>
+    <col min="2" max="2" width="18.5" style="102" customWidth="1"/>
+    <col min="3" max="3" width="28.1640625" style="102" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" style="102" customWidth="1"/>
+    <col min="5" max="5" width="43" style="102" customWidth="1"/>
+    <col min="6" max="6" width="3.6640625" style="102" customWidth="1"/>
+    <col min="7" max="7" width="21.1640625" style="102" customWidth="1"/>
+    <col min="8" max="8" width="4.1640625" style="102" customWidth="1"/>
+    <col min="9" max="9" width="21.1640625" style="102" customWidth="1"/>
+    <col min="10" max="16384" width="11" style="102"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" s="62" customFormat="1" ht="8" customHeight="1">
       <c r="C1" s="63"/>
       <c r="I1" s="67"/>
-      <c r="J1" s="99"/>
+      <c r="J1" s="98"/>
     </row>
     <row r="2" spans="2:10" s="62" customFormat="1" ht="15" customHeight="1">
-      <c r="B2" s="194" t="s">
+      <c r="B2" s="195" t="s">
         <v>134</v>
       </c>
-      <c r="C2" s="194"/>
-      <c r="D2" s="194"/>
-      <c r="E2" s="194"/>
-      <c r="F2" s="194"/>
-      <c r="G2" s="194"/>
-      <c r="H2" s="194"/>
-      <c r="I2" s="194"/>
-      <c r="J2" s="99"/>
+      <c r="C2" s="195"/>
+      <c r="D2" s="195"/>
+      <c r="E2" s="195"/>
+      <c r="F2" s="195"/>
+      <c r="G2" s="195"/>
+      <c r="H2" s="195"/>
+      <c r="I2" s="195"/>
+      <c r="J2" s="98"/>
     </row>
     <row r="3" spans="2:10" s="62" customFormat="1" ht="15" customHeight="1">
-      <c r="B3" s="194"/>
-      <c r="C3" s="194"/>
-      <c r="D3" s="194"/>
-      <c r="E3" s="194"/>
-      <c r="F3" s="194"/>
-      <c r="G3" s="194"/>
-      <c r="H3" s="194"/>
-      <c r="I3" s="194"/>
-      <c r="J3" s="99"/>
+      <c r="B3" s="195"/>
+      <c r="C3" s="195"/>
+      <c r="D3" s="195"/>
+      <c r="E3" s="195"/>
+      <c r="F3" s="195"/>
+      <c r="G3" s="195"/>
+      <c r="H3" s="195"/>
+      <c r="I3" s="195"/>
+      <c r="J3" s="98"/>
     </row>
     <row r="4" spans="2:10" s="62" customFormat="1" ht="12" customHeight="1">
-      <c r="B4" s="100"/>
-      <c r="C4" s="100"/>
-      <c r="D4" s="100"/>
-      <c r="E4" s="100"/>
-      <c r="F4" s="100"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="100"/>
-      <c r="I4" s="113"/>
-      <c r="J4" s="99"/>
+      <c r="B4" s="99"/>
+      <c r="C4" s="99"/>
+      <c r="D4" s="99"/>
+      <c r="E4" s="99"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="99"/>
+      <c r="H4" s="99"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="98"/>
     </row>
     <row r="5" spans="2:10" s="62" customFormat="1">
-      <c r="B5" s="101" t="s">
+      <c r="B5" s="100" t="s">
         <v>21</v>
       </c>
       <c r="C5" s="62">
@@ -76371,16 +76373,16 @@
       <c r="D5" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="102">
+      <c r="E5" s="101">
         <f>'Account Overview'!I5</f>
         <v>0</v>
       </c>
-      <c r="H5" s="211"/>
-      <c r="I5" s="211"/>
-      <c r="J5" s="99"/>
+      <c r="H5" s="210"/>
+      <c r="I5" s="210"/>
+      <c r="J5" s="98"/>
     </row>
     <row r="6" spans="2:10" s="62" customFormat="1">
-      <c r="B6" s="101" t="s">
+      <c r="B6" s="100" t="s">
         <v>23</v>
       </c>
       <c r="C6" s="62">
@@ -76390,238 +76392,233 @@
       <c r="D6" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="98">
+      <c r="E6" s="97">
         <f ca="1">TODAY()</f>
-        <v>46142</v>
+        <v>46143</v>
       </c>
-      <c r="H6" s="211"/>
-      <c r="I6" s="211"/>
-      <c r="J6" s="99"/>
+      <c r="H6" s="210"/>
+      <c r="I6" s="210"/>
+      <c r="J6" s="98"/>
     </row>
     <row r="7" spans="2:10" s="62" customFormat="1" ht="10" customHeight="1">
       <c r="C7" s="63"/>
-      <c r="H7" s="211"/>
-      <c r="I7" s="211"/>
-      <c r="J7" s="99"/>
+      <c r="H7" s="210"/>
+      <c r="I7" s="210"/>
+      <c r="J7" s="98"/>
     </row>
     <row r="8" spans="2:10" ht="30" customHeight="1" thickBot="1">
-      <c r="B8" s="208" t="s">
+      <c r="B8" s="207" t="s">
         <v>106</v>
       </c>
-      <c r="C8" s="208"/>
-      <c r="D8" s="208"/>
-      <c r="E8" s="208"/>
-      <c r="F8" s="208"/>
-      <c r="G8" s="208"/>
-      <c r="H8" s="212"/>
-      <c r="I8" s="212"/>
+      <c r="C8" s="207"/>
+      <c r="D8" s="207"/>
+      <c r="E8" s="207"/>
+      <c r="F8" s="207"/>
+      <c r="G8" s="207"/>
+      <c r="H8" s="211"/>
+      <c r="I8" s="211"/>
     </row>
     <row r="9" spans="2:10" ht="55" customHeight="1">
-      <c r="B9" s="114" t="s">
+      <c r="B9" s="113" t="s">
         <v>107</v>
       </c>
-      <c r="C9" s="104" t="s">
+      <c r="C9" s="103" t="s">
         <v>79</v>
       </c>
-      <c r="D9" s="209" t="s">
+      <c r="D9" s="208" t="s">
         <v>108</v>
       </c>
-      <c r="E9" s="209"/>
-      <c r="F9" s="209"/>
-      <c r="G9" s="209"/>
-      <c r="H9" s="209"/>
-      <c r="I9" s="210"/>
+      <c r="E9" s="208"/>
+      <c r="F9" s="208"/>
+      <c r="G9" s="208"/>
+      <c r="H9" s="208"/>
+      <c r="I9" s="209"/>
     </row>
     <row r="10" spans="2:10" ht="15" customHeight="1"/>
     <row r="11" spans="2:10" ht="30" customHeight="1" thickBot="1">
-      <c r="B11" s="208" t="s">
+      <c r="B11" s="207" t="s">
         <v>109</v>
       </c>
-      <c r="C11" s="208"/>
-      <c r="D11" s="208"/>
-      <c r="E11" s="208"/>
+      <c r="C11" s="207"/>
+      <c r="D11" s="207"/>
+      <c r="E11" s="207"/>
     </row>
     <row r="12" spans="2:10" ht="25" customHeight="1">
-      <c r="B12" s="116" t="s">
+      <c r="B12" s="115" t="s">
         <v>110</v>
       </c>
-      <c r="C12" s="117" t="s">
+      <c r="C12" s="116" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="196" t="s">
+      <c r="D12" s="197" t="s">
         <v>15</v>
       </c>
-      <c r="E12" s="197"/>
-      <c r="G12" s="123" t="s">
+      <c r="E12" s="198"/>
+      <c r="G12" s="122" t="s">
         <v>111</v>
       </c>
-      <c r="I12" s="123" t="s">
+      <c r="I12" s="122" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="13" spans="2:10" ht="55" customHeight="1">
-      <c r="B13" s="115" t="s">
+      <c r="B13" s="114" t="s">
         <v>113</v>
       </c>
-      <c r="C13" s="105" t="s">
+      <c r="C13" s="104" t="s">
         <v>80</v>
       </c>
-      <c r="D13" s="204" t="s">
+      <c r="D13" s="189" t="s">
         <v>135</v>
       </c>
-      <c r="E13" s="205"/>
-      <c r="G13" s="110" t="s">
+      <c r="E13" s="190"/>
+      <c r="G13" s="109" t="s">
         <v>79</v>
       </c>
-      <c r="I13" s="110" t="s">
+      <c r="I13" s="109" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="14" spans="2:10" ht="55" customHeight="1">
-      <c r="B14" s="118" t="s">
+      <c r="B14" s="117" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="105" t="s">
+      <c r="C14" s="104" t="s">
         <v>77</v>
       </c>
-      <c r="D14" s="202" t="s">
+      <c r="D14" s="203" t="s">
         <v>115</v>
       </c>
-      <c r="E14" s="203"/>
-      <c r="G14" s="111" t="s">
+      <c r="E14" s="204"/>
+      <c r="G14" s="110" t="s">
         <v>77</v>
       </c>
-      <c r="I14" s="111" t="s">
+      <c r="I14" s="110" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="15" spans="2:10" ht="55" customHeight="1" thickBot="1">
-      <c r="B15" s="115" t="s">
+      <c r="B15" s="114" t="s">
         <v>116</v>
       </c>
-      <c r="C15" s="105" t="s">
+      <c r="C15" s="104" t="s">
         <v>79</v>
       </c>
-      <c r="D15" s="204" t="s">
+      <c r="D15" s="189" t="s">
         <v>117</v>
       </c>
-      <c r="E15" s="205"/>
-      <c r="F15" s="107"/>
-      <c r="G15" s="112" t="s">
+      <c r="E15" s="190"/>
+      <c r="F15" s="106"/>
+      <c r="G15" s="111" t="s">
         <v>72</v>
       </c>
-      <c r="I15" s="112" t="s">
+      <c r="I15" s="111" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="16" spans="2:10" ht="55" customHeight="1">
-      <c r="B16" s="118" t="s">
+      <c r="B16" s="117" t="s">
         <v>118</v>
       </c>
-      <c r="C16" s="105" t="s">
+      <c r="C16" s="104" t="s">
         <v>77</v>
       </c>
-      <c r="D16" s="202" t="s">
+      <c r="D16" s="203" t="s">
         <v>119</v>
       </c>
-      <c r="E16" s="203"/>
-      <c r="F16" s="108"/>
-      <c r="H16" s="108"/>
+      <c r="E16" s="204"/>
+      <c r="F16" s="107"/>
+      <c r="H16" s="107"/>
     </row>
     <row r="17" spans="2:8" ht="55" customHeight="1">
-      <c r="B17" s="115" t="s">
+      <c r="B17" s="114" t="s">
         <v>120</v>
       </c>
-      <c r="C17" s="105" t="s">
+      <c r="C17" s="104" t="s">
         <v>77</v>
       </c>
-      <c r="D17" s="206" t="s">
+      <c r="D17" s="205" t="s">
         <v>121</v>
       </c>
-      <c r="E17" s="207"/>
-      <c r="F17" s="108"/>
-      <c r="H17" s="108"/>
+      <c r="E17" s="206"/>
+      <c r="F17" s="107"/>
+      <c r="H17" s="107"/>
     </row>
     <row r="18" spans="2:8" ht="55" customHeight="1" thickBot="1">
-      <c r="B18" s="119" t="s">
+      <c r="B18" s="118" t="s">
         <v>122</v>
       </c>
-      <c r="C18" s="109" t="s">
+      <c r="C18" s="108" t="s">
         <v>72</v>
       </c>
-      <c r="D18" s="200" t="s">
+      <c r="D18" s="201" t="s">
         <v>123</v>
       </c>
-      <c r="E18" s="201"/>
-      <c r="F18" s="108"/>
-      <c r="H18" s="108"/>
+      <c r="E18" s="202"/>
+      <c r="F18" s="107"/>
+      <c r="H18" s="107"/>
     </row>
     <row r="19" spans="2:8" ht="18" customHeight="1">
-      <c r="E19" s="106"/>
+      <c r="E19" s="105"/>
     </row>
     <row r="20" spans="2:8" ht="30" customHeight="1" thickBot="1">
-      <c r="B20" s="195" t="s">
+      <c r="B20" s="196" t="s">
         <v>136</v>
       </c>
-      <c r="C20" s="195"/>
-      <c r="D20" s="195"/>
-      <c r="E20" s="195"/>
+      <c r="C20" s="196"/>
+      <c r="D20" s="196"/>
+      <c r="E20" s="196"/>
     </row>
     <row r="21" spans="2:8" ht="25" customHeight="1">
-      <c r="B21" s="116" t="s">
+      <c r="B21" s="115" t="s">
         <v>137</v>
       </c>
-      <c r="C21" s="117" t="s">
+      <c r="C21" s="116" t="s">
         <v>18</v>
       </c>
-      <c r="D21" s="196" t="s">
+      <c r="D21" s="197" t="s">
         <v>126</v>
       </c>
-      <c r="E21" s="197"/>
+      <c r="E21" s="198"/>
     </row>
     <row r="22" spans="2:8" ht="58" customHeight="1">
-      <c r="B22" s="122" t="s">
+      <c r="B22" s="121" t="s">
         <v>138</v>
       </c>
-      <c r="C22" s="105" t="s">
+      <c r="C22" s="104" t="s">
         <v>79</v>
       </c>
-      <c r="D22" s="198" t="s">
+      <c r="D22" s="199" t="s">
         <v>139</v>
       </c>
-      <c r="E22" s="199"/>
+      <c r="E22" s="200"/>
     </row>
     <row r="23" spans="2:8" ht="58" customHeight="1">
-      <c r="B23" s="121" t="s">
+      <c r="B23" s="120" t="s">
         <v>140</v>
       </c>
-      <c r="C23" s="105" t="s">
+      <c r="C23" s="104" t="s">
         <v>77</v>
       </c>
-      <c r="D23" s="190" t="s">
+      <c r="D23" s="191" t="s">
         <v>141</v>
       </c>
-      <c r="E23" s="191"/>
+      <c r="E23" s="192"/>
     </row>
     <row r="24" spans="2:8" ht="58" customHeight="1" thickBot="1">
-      <c r="B24" s="120" t="s">
+      <c r="B24" s="119" t="s">
         <v>142</v>
       </c>
-      <c r="C24" s="109" t="s">
+      <c r="C24" s="108" t="s">
         <v>72</v>
       </c>
-      <c r="D24" s="192" t="s">
+      <c r="D24" s="193" t="s">
         <v>143</v>
       </c>
-      <c r="E24" s="193"/>
+      <c r="E24" s="194"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="D24:E24"/>
     <mergeCell ref="D17:E17"/>
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="B2:I3"/>
@@ -76634,6 +76631,11 @@
     <mergeCell ref="D14:E14"/>
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="D16:E16"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D24:E24"/>
   </mergeCells>
   <conditionalFormatting sqref="C9 C13:C18 C22:C24">
     <cfRule type="containsText" dxfId="6" priority="5" operator="containsText" text="At Risk">
@@ -76673,26 +76675,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="a5ccdd2c-0fa4-45e2-a986-571ffa658233" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f30d6940-85d6-4319-8658-7b5d199f76fb">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D320D4CDE0E3CF4CAC53E9BAA4534025" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="25d2eab2951692af2de58fca8d59a9b6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f30d6940-85d6-4319-8658-7b5d199f76fb" xmlns:ns3="a5ccdd2c-0fa4-45e2-a986-571ffa658233" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="45d87c22090faa6df3c8e2be76bedf14" ns2:_="" ns3:_="">
     <xsd:import namespace="f30d6940-85d6-4319-8658-7b5d199f76fb"/>
@@ -76921,26 +76903,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FDEB5687-A511-489E-818B-D75BA96C26C7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="a5ccdd2c-0fa4-45e2-a986-571ffa658233"/>
-    <ds:schemaRef ds:uri="f30d6940-85d6-4319-8658-7b5d199f76fb"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6E9AEEC-7C7B-49A4-BC3A-CF23115A58E2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="a5ccdd2c-0fa4-45e2-a986-571ffa658233" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f30d6940-85d6-4319-8658-7b5d199f76fb">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FAA6C6C1-C134-46C1-AB67-8670CF0E614F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -76957,4 +76940,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6E9AEEC-7C7B-49A4-BC3A-CF23115A58E2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FDEB5687-A511-489E-818B-D75BA96C26C7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="a5ccdd2c-0fa4-45e2-a986-571ffa658233"/>
+    <ds:schemaRef ds:uri="f30d6940-85d6-4319-8658-7b5d199f76fb"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>